--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3CF23D-8821-427D-B3D2-D6CE2D714A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D98AB6-DC49-4242-A3C7-7BA04EC48D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="281">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -327,16 +327,7 @@
     <t>Contêiner</t>
   </si>
   <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Produzido</t>
-  </si>
-  <si>
     <t>Informação</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informção de acordo à norma NBR 19650-1.</t>
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
@@ -383,9 +374,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard.</t>
-  </si>
-  <si>
     <t>CTI_Projeto_01</t>
   </si>
   <si>
@@ -888,6 +876,45 @@
   </si>
   <si>
     <t>Reserva.Intermediária</t>
+  </si>
+  <si>
+    <t>Definida</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Requerida</t>
+  </si>
+  <si>
+    <t>No.Projeto</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>Requisito.Espacial</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Mobiliário</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Equipamento</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Sistemas</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
 </sst>
 </file>
@@ -995,12 +1022,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2AA84"/>
         <bgColor rgb="FFF6C6AD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E896"/>
-        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1117,6 +1138,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9F2D0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1230,24 +1257,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1263,10 +1290,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1278,28 +1305,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1308,34 +1335,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1344,7 +1368,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1359,7 +1383,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1371,7 +1395,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1389,29 +1413,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1422,20 +1443,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1499,6 +1528,46 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1634,13 +1703,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2077,10 +2144,10 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="40.07421875" style="64" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="64"/>
+    <col min="1" max="1" width="8.69140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="40.07421875" style="62" customWidth="1"/>
+    <col min="3" max="3" width="3.4609375" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2090,8 +2157,8 @@
       <c r="B1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="44" t="s">
-        <v>96</v>
+      <c r="C1" s="43" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2101,8 +2168,8 @@
       <c r="B2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="45" t="s">
-        <v>97</v>
+      <c r="C2" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2110,10 +2177,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>97</v>
+        <v>124</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2123,8 +2190,8 @@
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>97</v>
+      <c r="C4" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2135,8 +2202,8 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>97</v>
+      <c r="C5" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2147,8 +2214,8 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>97</v>
+      <c r="C6" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2158,19 +2225,19 @@
       <c r="B7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="42" t="s">
+      <c r="C7" s="44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="44" t="s">
         <v>94</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2180,8 +2247,8 @@
       <c r="B9" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>97</v>
+      <c r="C9" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2191,8 +2258,8 @@
       <c r="B10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>97</v>
+      <c r="C10" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2202,8 +2269,8 @@
       <c r="B11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="45" t="s">
-        <v>97</v>
+      <c r="C11" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2213,8 +2280,8 @@
       <c r="B12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>97</v>
+      <c r="C12" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2224,8 +2291,8 @@
       <c r="B13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="45" t="s">
-        <v>97</v>
+      <c r="C13" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2235,8 +2302,8 @@
       <c r="B14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>97</v>
+      <c r="C14" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2246,8 +2313,8 @@
       <c r="B15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="45" t="s">
-        <v>97</v>
+      <c r="C15" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2257,8 +2324,8 @@
       <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>97</v>
+      <c r="C16" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2266,10 +2333,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>97</v>
+        <v>125</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2278,10 +2345,10 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46134.927114814818</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>97</v>
+        <v>46139.499703125002</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2291,8 +2358,8 @@
       <c r="B19" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="45" t="s">
-        <v>97</v>
+      <c r="C19" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2302,8 +2369,8 @@
       <c r="B20" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="45" t="s">
-        <v>97</v>
+      <c r="C20" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2313,8 +2380,8 @@
       <c r="B21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="45" t="s">
-        <v>97</v>
+      <c r="C21" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2322,10 +2389,10 @@
         <v>72</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>97</v>
+        <v>126</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2333,22 +2400,22 @@
         <v>73</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>127</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Fire Fighting Objects</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>99</v>
+      <c r="C24" s="44" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2426,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.84375" bestFit="1" customWidth="1"/>
@@ -2367,8 +2434,8 @@
     <col min="3" max="3" width="7.4609375" customWidth="1"/>
     <col min="4" max="4" width="7.07421875" customWidth="1"/>
     <col min="5" max="5" width="9.84375" customWidth="1"/>
-    <col min="6" max="6" width="10.765625" style="47" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="37" customWidth="1"/>
+    <col min="6" max="6" width="10.765625" style="46" customWidth="1"/>
+    <col min="7" max="11" width="6.3046875" style="36" customWidth="1"/>
     <col min="12" max="12" width="7.4609375" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
     <col min="14" max="14" width="9.61328125" customWidth="1"/>
@@ -2376,98 +2443,98 @@
     <col min="16" max="16" width="49.53515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="30.53515625" customWidth="1"/>
     <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.921875" customWidth="1"/>
+    <col min="19" max="19" width="7.61328125" customWidth="1"/>
     <col min="20" max="20" width="7.23046875" customWidth="1"/>
-    <col min="21" max="21" width="8.84375" customWidth="1"/>
+    <col min="21" max="21" width="10.69140625" customWidth="1"/>
     <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="9" style="62" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="53.07421875" style="62" customWidth="1"/>
-    <col min="25" max="25" width="22.07421875" style="63" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="62" customWidth="1"/>
+    <col min="23" max="23" width="6.15234375" style="60" customWidth="1"/>
+    <col min="24" max="24" width="53.07421875" style="60" customWidth="1"/>
+    <col min="25" max="25" width="22.07421875" style="61" customWidth="1"/>
+    <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
     <col min="27" max="27" width="44.69140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="50" t="s">
+      <c r="A1" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="40" t="s">
+      <c r="L1" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="P1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="S1" s="40" t="s">
+      <c r="R1" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="S1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="T1" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="53" t="s">
+      <c r="U1" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="V1" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="66" t="s">
+      <c r="W1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="40" t="s">
+      <c r="X1" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z1" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA1" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="Y1" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z1" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" s="41" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2475,76 +2542,77 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="33" t="str">
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="M2" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N2" s="33" t="str">
+        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Definida</v>
+      </c>
+      <c r="O2" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No Projeto</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="34" t="str">
-        <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="34" t="str">
-        <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
-        <v>Produzido</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="O2" s="30" t="str">
-        <f t="shared" ref="O2" si="2">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("Categ.  Rvt:   ",F2))</f>
-        <v>Categ.  Rvt:   Contêiner</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="36" t="str">
-        <f t="shared" ref="T2" si="3">SUBSTITUTE(D2, "_", " ")</f>
-        <v>Produzido</v>
-      </c>
-      <c r="U2" s="36" t="str">
-        <f t="shared" ref="U2" si="4">SUBSTITUTE(E2, "_", " ")</f>
+      <c r="R2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="35" t="str">
+        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="T2" s="35" t="str">
+        <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="V2" s="36" t="str">
-        <f t="shared" ref="V2" si="5">SUBSTITUTE(C2, "_", " ")</f>
-        <v>Gestão</v>
-      </c>
-      <c r="W2" s="67" t="str">
-        <f>CONCATENATE("Key-INC-",A2)</f>
+      <c r="U2" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Definida</v>
+      </c>
+      <c r="V2" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W2" s="65" t="str">
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
       <c r="X2" s="30" t="s">
@@ -2553,11 +2621,12 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="30" t="s">
-        <v>103</v>
+      <c r="Z2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="30" t="str">
+        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2565,448 +2634,456 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>115</v>
+        <v>272</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="34" t="str">
-        <f t="shared" ref="L3" si="6">CONCATENATE("", C3)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M3" s="34" t="str">
-        <f t="shared" ref="M3" si="7">CONCATENATE("", D3)</f>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="O3" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="P3" s="59" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q3" s="59" t="s">
-        <v>266</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="36" t="str">
-        <f t="shared" ref="S3:U18" si="8">SUBSTITUTE(C3, ".", " ")</f>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T3" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U3" s="36" t="str">
-        <f t="shared" ref="U3" si="9">SUBSTITUTE(E3, "_", " ")</f>
-        <v>Sistema.Combate</v>
-      </c>
-      <c r="V3" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" s="67" t="str">
-        <f t="shared" ref="W3:W24" si="10">CONCATENATE("Key-INC-",A3)</f>
+        <v>85</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M3" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N3" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O3" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Espacial</v>
+      </c>
+      <c r="P3" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T3" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U3" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V3" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W3" s="65" t="str">
+        <f t="shared" si="3"/>
         <v>Key-INC-3</v>
       </c>
-      <c r="X3" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z3" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA3" s="30" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="X3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="32">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>115</v>
+        <v>272</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="34" t="str">
-        <f t="shared" ref="L4:M19" si="11">CONCATENATE("", C4)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M4" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N4" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O4" s="34" t="str">
-        <f t="shared" ref="O4:O17" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F4),"."," ")," De "," de "))</f>
-        <v>Alarme</v>
+        <v>270</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M4" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N4" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O4" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T4" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U4" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W4" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="R4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V4" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W4" s="65" t="str">
+        <f t="shared" si="3"/>
         <v>Key-INC-4</v>
       </c>
       <c r="X4" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z4" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA4" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="32">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>115</v>
+        <v>272</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F5" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M5" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O5" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Campainha</v>
+        <v>270</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M5" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N5" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O5" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>143</v>
+        <v>278</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T5" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U5" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W5" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W5" s="65" t="str">
+        <f t="shared" si="3"/>
         <v>Key-INC-5</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y5" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z5" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="32">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>115</v>
+        <v>272</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M6" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O6" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Campainha Caixa</v>
+        <v>270</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M6" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N6" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O6" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>146</v>
+        <v>280</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="R6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T6" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U6" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="V6" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W6" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V6" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W6" s="65" t="str">
+        <f t="shared" si="3"/>
         <v>Key-INC-6</v>
       </c>
       <c r="X6" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y6" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z6" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="32">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="48" t="s">
-        <v>115</v>
+      <c r="C7" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F7" s="65" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="34" t="str">
-        <f t="shared" si="11"/>
+        <v>130</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="33" t="str">
+        <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M7" s="34" t="str">
-        <f t="shared" si="11"/>
+      <c r="M7" s="33" t="str">
+        <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N7" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O7" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Lumínico</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="R7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="36" t="str">
+      <c r="N7" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="P7" s="58" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q7" s="58" t="s">
+        <v>262</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="35" t="str">
+        <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, ".", " ")</f>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T7" s="35" t="str">
+        <f t="shared" ref="T7:U20" si="8">SUBSTITUTE(D7, ".", " ")</f>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U7" s="35" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T7" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U7" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="V7" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W7" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>Sistema Combate</v>
+      </c>
+      <c r="V7" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W7" s="65" t="str">
+        <f t="shared" ref="W7:W28" si="9">CONCATENATE("Key-INC-",A7)</f>
         <v>Key-INC-7</v>
       </c>
-      <c r="X7" s="30" t="s">
-        <v>184</v>
+      <c r="X7" s="29" t="s">
+        <v>119</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z7" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA7" s="30" t="s">
         <v>263</v>
-      </c>
-      <c r="AA7" s="30" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3016,87 +3093,87 @@
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="48" t="s">
-        <v>115</v>
+      <c r="C8" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="34" t="str">
-        <f t="shared" si="11"/>
+        <v>264</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="33" t="str">
+        <f t="shared" ref="L8:M23" si="10">CONCATENATE("", C8)</f>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M8" s="34" t="str">
-        <f t="shared" si="11"/>
+      <c r="M8" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N8" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O8" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Caixa Manual</v>
+      <c r="N8" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O8" s="33" t="str">
+        <f t="shared" ref="O8:O21" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
+        <v>Alarme</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>137</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T8" s="36" t="str">
+      <c r="T8" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U8" s="36" t="str">
+      <c r="U8" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V8" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W8" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V8" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W8" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-8</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="Z8" s="30" t="s">
-        <v>263</v>
+        <v>188</v>
+      </c>
+      <c r="Z8" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3106,87 +3183,87 @@
       <c r="B9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="48" t="s">
-        <v>115</v>
+      <c r="C9" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F9" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M9" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O9" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M9" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O9" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Detonador</v>
+        <v>Alarme Campainha</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>140</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T9" s="36" t="str">
+      <c r="T9" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U9" s="36" t="str">
+      <c r="U9" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V9" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W9" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V9" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W9" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z9" s="30" t="s">
-        <v>263</v>
+        <v>189</v>
+      </c>
+      <c r="Z9" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3196,87 +3273,87 @@
       <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>115</v>
+      <c r="C10" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F10" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M10" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O10" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M10" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O10" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Sirene</v>
+        <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>143</v>
+      </c>
+      <c r="R10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T10" s="36" t="str">
+      <c r="T10" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U10" s="36" t="str">
+      <c r="U10" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V10" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W10" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V10" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W10" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z10" s="30" t="s">
-        <v>263</v>
+        <v>190</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3286,87 +3363,87 @@
       <c r="B11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>115</v>
+      <c r="C11" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F11" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M11" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O11" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M11" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="O11" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Alarme Apito</v>
+        <v>Alarme Lumínico</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>146</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T11" s="36" t="str">
+      <c r="T11" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U11" s="36" t="str">
+      <c r="U11" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V11" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W11" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V11" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W11" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z11" s="30" t="s">
-        <v>263</v>
+        <v>191</v>
+      </c>
+      <c r="Z11" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3376,87 +3453,87 @@
       <c r="B12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>115</v>
+      <c r="C12" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M12" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O12" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M12" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N12" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O12" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Terminal Combate Fogo</v>
+        <v>Alarme Caixa Manual</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>149</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T12" s="36" t="str">
+      <c r="T12" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U12" s="36" t="str">
+      <c r="U12" s="35" t="str">
         <f t="shared" si="8"/>
-        <v>Peças de Incêndio</v>
-      </c>
-      <c r="V12" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W12" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>Alarmes de Incêndio</v>
+      </c>
+      <c r="V12" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W12" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z12" s="30" t="s">
-        <v>263</v>
+        <v>192</v>
+      </c>
+      <c r="Z12" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3466,87 +3543,87 @@
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>115</v>
+      <c r="C13" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M13" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O13" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M13" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N13" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O13" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Mangueira Entrada</v>
+        <v>Alarme Detonador</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>152</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T13" s="36" t="str">
+      <c r="T13" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U13" s="36" t="str">
+      <c r="U13" s="35" t="str">
         <f t="shared" si="8"/>
-        <v>Peças de Incêndio</v>
-      </c>
-      <c r="V13" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W13" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>Alarmes de Incêndio</v>
+      </c>
+      <c r="V13" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W13" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z13" s="30" t="s">
-        <v>263</v>
+        <v>193</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3556,87 +3633,87 @@
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="48" t="s">
-        <v>115</v>
+      <c r="C14" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F14" s="65" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M14" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O14" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M14" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N14" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O14" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Mangueira Carretel</v>
+        <v>Alarme Sirene</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="R14" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>155</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T14" s="36" t="str">
+      <c r="T14" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U14" s="36" t="str">
+      <c r="U14" s="35" t="str">
         <f t="shared" si="8"/>
-        <v>Peças de Incêndio</v>
-      </c>
-      <c r="V14" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W14" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>Alarmes de Incêndio</v>
+      </c>
+      <c r="V14" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W14" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z14" s="30" t="s">
-        <v>263</v>
+        <v>194</v>
+      </c>
+      <c r="Z14" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3646,87 +3723,87 @@
       <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="48" t="s">
-        <v>115</v>
+      <c r="C15" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F15" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="34" t="str">
+        <v>264</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M15" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O15" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M15" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N15" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O15" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Mangueira Canhão</v>
+        <v>Alarme Apito</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>158</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T15" s="36" t="str">
+      <c r="T15" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U15" s="36" t="str">
+      <c r="U15" s="35" t="str">
         <f t="shared" si="8"/>
-        <v>Peças de Incêndio</v>
-      </c>
-      <c r="V15" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W15" s="67" t="str">
-        <f t="shared" si="10"/>
+        <v>Alarmes de Incêndio</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W15" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z15" s="30" t="s">
-        <v>263</v>
+        <v>195</v>
+      </c>
+      <c r="Z15" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3736,87 +3813,87 @@
       <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>115</v>
+      <c r="C16" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F16" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="34" t="str">
+        <v>265</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O16" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M16" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N16" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O16" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Hidrante</v>
+        <v>Terminal Combate Fogo</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="R16" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>161</v>
+      </c>
+      <c r="R16" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T16" s="36" t="str">
+      <c r="T16" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U16" s="36" t="str">
+      <c r="U16" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V16" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W16" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V16" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W16" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z16" s="30" t="s">
-        <v>263</v>
+        <v>184</v>
+      </c>
+      <c r="Z16" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3826,87 +3903,87 @@
       <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>115</v>
+      <c r="C17" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F17" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="34" t="str">
+        <v>265</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O17" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M17" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N17" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O17" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v>Sprinkler</v>
+        <v>Mangueira Entrada</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="R17" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>164</v>
+      </c>
+      <c r="R17" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T17" s="36" t="str">
+      <c r="T17" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U17" s="36" t="str">
+      <c r="U17" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V17" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W17" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V17" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W17" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z17" s="30" t="s">
-        <v>263</v>
+        <v>196</v>
+      </c>
+      <c r="Z17" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3916,446 +3993,446 @@
       <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>115</v>
+      <c r="C18" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="34" t="str">
+        <v>265</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M18" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O18" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M18" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N18" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>257</v>
+        <v>Mangueira Carretel</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="36" t="str">
-        <f t="shared" si="8"/>
+        <v>167</v>
+      </c>
+      <c r="R18" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T18" s="36" t="str">
+      <c r="T18" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U18" s="36" t="str">
+      <c r="U18" s="35" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V18" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W18" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V18" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W18" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z18" s="30" t="s">
-        <v>263</v>
+        <v>197</v>
+      </c>
+      <c r="Z18" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="32">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="48" t="s">
-        <v>115</v>
+      <c r="C19" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="34" t="str">
+        <v>265</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M19" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N19" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O19" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M19" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N19" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="O19" s="59" t="s">
-        <v>251</v>
-      </c>
-      <c r="P19" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q19" s="30" t="str">
-        <f t="shared" ref="Q19" si="13">_xlfn.TRANSLATE(P19,"pt","es")</f>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="36" t="str">
-        <f t="shared" ref="S19:T23" si="14">SUBSTITUTE(C19, ".", " ")</f>
+        <v>Mangueira Canhão</v>
+      </c>
+      <c r="P19" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q19" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="R19" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T19" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="T19" s="35" t="str">
+        <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U19" s="36" t="str">
-        <f t="shared" ref="U19:U23" si="15">SUBSTITUTE(E19, ".", " ")</f>
+      <c r="U19" s="35" t="str">
+        <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V19" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W19" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="V19" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W19" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z19" s="30" t="s">
-        <v>263</v>
+        <v>198</v>
+      </c>
+      <c r="Z19" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="32">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="48" t="s">
-        <v>115</v>
+      <c r="C20" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" s="34" t="str">
-        <f t="shared" ref="L20:L23" si="16">CONCATENATE("", C20)</f>
+        <v>130</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M20" s="34" t="str">
-        <f t="shared" ref="M20:M23" si="17">CONCATENATE("", D20)</f>
+      <c r="M20" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N20" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="O20" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="P20" s="59" t="s">
+      <c r="N20" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O20" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Hidrante</v>
+      </c>
+      <c r="P20" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q20" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="R20" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="35" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T20" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U20" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v>Peças de Incêndio</v>
+      </c>
+      <c r="V20" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="Q20" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
-        <v>Cisterna Superior</v>
-      </c>
-      <c r="R20" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="36" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T20" s="36" t="str">
-        <f t="shared" si="14"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U20" s="36" t="str">
-        <f t="shared" si="15"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V20" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W20" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="W20" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-20</v>
       </c>
-      <c r="X20" s="29" t="s">
-        <v>112</v>
+      <c r="X20" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z20" s="30" t="s">
-        <v>263</v>
+        <v>199</v>
+      </c>
+      <c r="Z20" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="32">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="48" t="s">
-        <v>115</v>
+      <c r="C21" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F21" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>271</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L21" s="34" t="str">
-        <f t="shared" si="16"/>
+      <c r="G21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L21" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M21" s="34" t="str">
-        <f t="shared" si="17"/>
+      <c r="M21" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N21" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="O21" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="P21" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q21" s="30" t="str">
-        <f t="shared" ref="Q21:Q23" si="18">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Cisterna intermedia</v>
-      </c>
-      <c r="R21" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="N21" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O21" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Sprinkler</v>
+      </c>
+      <c r="P21" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q21" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="R21" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T21" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="T21" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U21" s="36" t="str">
-        <f t="shared" si="15"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V21" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W21" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="U21" s="35" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças de Incêndio</v>
+      </c>
+      <c r="V21" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W21" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-21</v>
       </c>
-      <c r="X21" s="29" t="s">
-        <v>112</v>
+      <c r="X21" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z21" s="30" t="s">
-        <v>263</v>
+        <v>200</v>
+      </c>
+      <c r="Z21" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="32">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>115</v>
+      <c r="C22" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L22" s="34" t="str">
-        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L22" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M22" s="34" t="str">
-        <f t="shared" si="17"/>
+      <c r="M22" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N22" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="O22" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="P22" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q22" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Cisterna Inferior</v>
-      </c>
-      <c r="R22" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="N22" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O22" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q22" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="R22" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T22" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="T22" s="35" t="str">
+        <f t="shared" si="7"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U22" s="36" t="str">
-        <f t="shared" si="15"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V22" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W22" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="U22" s="35" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças de Incêndio</v>
+      </c>
+      <c r="V22" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W22" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-22</v>
       </c>
-      <c r="X22" s="29" t="s">
-        <v>112</v>
+      <c r="X22" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z22" s="30" t="s">
-        <v>263</v>
+        <v>201</v>
+      </c>
+      <c r="Z22" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4365,87 +4442,87 @@
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>115</v>
+      <c r="C23" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="34" t="str">
-        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M23" s="34" t="str">
-        <f t="shared" si="17"/>
+      <c r="M23" s="33" t="str">
+        <f t="shared" si="10"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N23" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="O23" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="P23" s="59" t="s">
-        <v>118</v>
+      <c r="N23" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="O23" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="P23" s="58" t="s">
+        <v>120</v>
       </c>
       <c r="Q23" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubería de agua fría</v>
-      </c>
-      <c r="R23" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="Q23" si="12">_xlfn.TRANSLATE(P23,"pt","es")</f>
+        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
+      </c>
+      <c r="R23" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="35" t="str">
+        <f t="shared" ref="S23:U28" si="13">SUBSTITUTE(C23, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
-      <c r="T23" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="T23" s="35" t="str">
+        <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U23" s="36" t="str">
-        <f t="shared" si="15"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V23" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W23" s="67" t="str">
-        <f t="shared" si="10"/>
+      <c r="U23" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças de Incêndio</v>
+      </c>
+      <c r="V23" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W23" s="65" t="str">
+        <f t="shared" si="9"/>
         <v>Key-INC-23</v>
       </c>
-      <c r="X23" s="29" t="s">
-        <v>112</v>
+      <c r="X23" s="30" t="s">
+        <v>182</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z23" s="30" t="s">
-        <v>263</v>
+        <v>184</v>
+      </c>
+      <c r="Z23" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4455,142 +4532,515 @@
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="33" t="str">
+        <f t="shared" ref="L24:L27" si="14">CONCATENATE("", C24)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M24" s="33" t="str">
+        <f t="shared" ref="M24:M27" si="15">CONCATENATE("", D24)</f>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N24" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="O24" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="P24" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q24" s="30" t="str">
+        <f>_xlfn.TRANSLATE(P24,"pt","es")</f>
+        <v>Cisterna Superior</v>
+      </c>
+      <c r="R24" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T24" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U24" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V24" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W24" s="65" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-INC-24</v>
+      </c>
+      <c r="X24" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y24" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z24" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA24" s="30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="32">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="33" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M25" s="33" t="str">
+        <f t="shared" si="15"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N25" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="O25" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="P25" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="34" t="str">
-        <f t="shared" ref="L24" si="19">CONCATENATE("", C24)</f>
+      <c r="Q25" s="30" t="str">
+        <f t="shared" ref="Q25:Q27" si="16">_xlfn.TRANSLATE(P25,"pt","es")</f>
+        <v>Cisterna intermedia</v>
+      </c>
+      <c r="R25" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T25" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U25" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V25" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W25" s="65" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-INC-25</v>
+      </c>
+      <c r="X25" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y25" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z25" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA25" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="32">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" si="14"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M24" s="34" t="str">
-        <f t="shared" ref="M24" si="20">CONCATENATE("", D24)</f>
+      <c r="M26" s="33" t="str">
+        <f t="shared" si="15"/>
         <v>Sis.Incêndio</v>
       </c>
-      <c r="N24" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="O24" s="59" t="s">
-        <v>256</v>
-      </c>
-      <c r="P24" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q24" s="30" t="str">
-        <f t="shared" ref="Q24" si="21">_xlfn.TRANSLATE(P24,"pt","es")</f>
+      <c r="N26" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="O26" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="P26" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q26" s="30" t="str">
+        <f t="shared" si="16"/>
+        <v>Cisterna Inferior</v>
+      </c>
+      <c r="R26" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T26" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U26" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V26" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W26" s="65" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-INC-26</v>
+      </c>
+      <c r="X26" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y26" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z26" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA26" s="30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" si="15"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N27" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="O27" s="58" t="s">
+        <v>251</v>
+      </c>
+      <c r="P27" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q27" s="30" t="str">
+        <f t="shared" si="16"/>
         <v>Tubería de agua fría</v>
       </c>
-      <c r="R24" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="36" t="str">
-        <f t="shared" ref="S24" si="22">SUBSTITUTE(C24, ".", " ")</f>
+      <c r="R27" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="35" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T24" s="36" t="str">
-        <f t="shared" ref="T24" si="23">SUBSTITUTE(D24, ".", " ")</f>
+      <c r="T27" s="35" t="str">
+        <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U24" s="36" t="str">
-        <f t="shared" ref="U24" si="24">SUBSTITUTE(E24, ".", " ")</f>
+      <c r="U27" s="35" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V24" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="W24" s="67" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-INC-24</v>
-      </c>
-      <c r="X24" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y24" s="29" t="s">
+      <c r="V27" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W27" s="65" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-INC-27</v>
+      </c>
+      <c r="X27" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y27" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z27" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA27" s="30" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA24" s="30" t="s">
-        <v>220</v>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" ref="L28" si="17">CONCATENATE("", C28)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" ref="M28" si="18">CONCATENATE("", D28)</f>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="O28" s="58" t="s">
+        <v>252</v>
+      </c>
+      <c r="P28" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q28" s="30" t="str">
+        <f t="shared" ref="Q28" si="19">_xlfn.TRANSLATE(P28,"pt","es")</f>
+        <v>Tubería de agua fría</v>
+      </c>
+      <c r="R28" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="35" t="str">
+        <f t="shared" ref="S28" si="20">SUBSTITUTE(C28, ".", " ")</f>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T28" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U28" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V28" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="W28" s="65" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-INC-28</v>
+      </c>
+      <c r="X28" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y28" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z28" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA28" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA891">
-    <sortCondition ref="F2:F891"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA895">
+    <sortCondition ref="F7:F895"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="21" priority="1490"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F3 F19:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="1512"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F18">
-    <cfRule type="duplicateValues" dxfId="18" priority="1534"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:F1048576 F2">
-    <cfRule type="duplicateValues" dxfId="17" priority="1483"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:F1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1462"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O13:O18 A1:D1 F1:O1 Q1:X1 Z1:AA1 S3:T3 E4:F12 L4:O12 B4:B18 Q4:Q18 X4:Y18 AA4:XFD18 S4:U24 F13:F18 L13:M18 E13:E19 N13:N19">
-    <cfRule type="cellIs" dxfId="13" priority="54" operator="equal">
+  <conditionalFormatting sqref="AA7">
+    <cfRule type="cellIs" dxfId="26" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="25" priority="1502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O19:O24">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  <conditionalFormatting sqref="F8:F22">
+    <cfRule type="duplicateValues" dxfId="24" priority="1546"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+  <conditionalFormatting sqref="F23:F1048576 F1 F7">
+    <cfRule type="duplicateValues" dxfId="23" priority="1524"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X19">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+  <conditionalFormatting sqref="F29:F1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1495"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O17:O22 A1:D1 F1:O1 Q1:X1 Z1:AA1 S7:S28 E8:F16 L8:O16 B8:B22 Q8:Q22 X8:Y22 AA8:XFD22 F17:F22 L17:M22 E17:E23 N17:N23">
+    <cfRule type="cellIs" dxfId="18" priority="66" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA3">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+  <conditionalFormatting sqref="O22">
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O23:O28">
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7">
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X23">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA19:AA24">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+  <conditionalFormatting sqref="AA23:AA28">
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A28">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4805,7 +5255,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4865,7 +5315,7 @@
       <c r="G1" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="54" t="s">
         <v>77</v>
       </c>
       <c r="I1" s="19" t="s">
@@ -4907,54 +5357,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="56" t="s">
+      <c r="L2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="56" t="s">
+      <c r="N2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="56" t="s">
+      <c r="P2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="56" t="s">
+      <c r="R2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="24" t="s">
@@ -4966,58 +5416,58 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="39" t="s">
-        <v>104</v>
+      <c r="E3" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="H3" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="J3" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="J3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="56" t="s">
+      <c r="N3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="56" t="s">
+      <c r="R3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5025,884 +5475,884 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="57" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="39" t="s">
-        <v>104</v>
+      <c r="E4" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="H4" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="H4" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="J4" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="J4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="56" t="s">
+      <c r="L4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="56" t="s">
+      <c r="N4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="Q4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="56" t="s">
+      <c r="R4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>227</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>225</v>
+      <c r="B5" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="H5" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P5" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="Q5" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="L5" s="56" t="s">
+      <c r="R5" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M5" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N5" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P5" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="R5" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>241</v>
+      <c r="B6" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N6" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="R6" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="S6" s="24" t="s">
         <v>245</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L6" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P6" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="R6" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="54" t="s">
-        <v>229</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="39" t="s">
+      <c r="B7" s="53" t="s">
         <v>225</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K7" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H7" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="56" t="s">
+      <c r="L7" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N7" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P7" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L7" s="56" t="s">
+      <c r="Q7" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R7" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M7" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N7" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R7" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S7" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>225</v>
+      <c r="B8" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H8" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="56" t="s">
+      <c r="L8" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P8" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L8" s="56" t="s">
+      <c r="Q8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R8" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M8" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N8" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P8" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R8" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S8" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>225</v>
+      <c r="B9" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H9" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H9" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="56" t="s">
+      <c r="L9" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P9" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L9" s="56" t="s">
+      <c r="Q9" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R9" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M9" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N9" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P9" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q9" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R9" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S9" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>9</v>
       </c>
-      <c r="B10" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>225</v>
+      <c r="B10" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H10" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="56" t="s">
+      <c r="L10" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N10" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P10" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L10" s="56" t="s">
+      <c r="Q10" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R10" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M10" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N10" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P10" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R10" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S10" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>225</v>
+      <c r="B11" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H11" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H11" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="56" t="s">
+      <c r="L11" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P11" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L11" s="56" t="s">
+      <c r="Q11" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R11" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M11" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N11" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P11" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q11" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R11" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S11" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="54" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>225</v>
+      <c r="B12" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>221</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H12" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K12" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H12" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="56" t="s">
+      <c r="L12" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P12" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L12" s="56" t="s">
+      <c r="Q12" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R12" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M12" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N12" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P12" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R12" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S12" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>12</v>
       </c>
-      <c r="B13" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>241</v>
+      <c r="B13" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H13" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H13" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="56" t="s">
+      <c r="J13" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L13" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N13" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P13" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L13" s="56" t="s">
+      <c r="Q13" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R13" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M13" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N13" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P13" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q13" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R13" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>13</v>
       </c>
-      <c r="B14" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>241</v>
+      <c r="B14" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H14" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H14" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J14" s="56" t="s">
+      <c r="J14" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L14" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N14" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P14" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L14" s="56" t="s">
+      <c r="Q14" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R14" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M14" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N14" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P14" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R14" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S14" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>14</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="38" t="s">
         <v>237</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>241</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H15" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J15" s="56" t="s">
+      <c r="J15" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L15" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O15" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P15" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L15" s="56" t="s">
+      <c r="Q15" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R15" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M15" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N15" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P15" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R15" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S15" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>15</v>
       </c>
-      <c r="B16" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>241</v>
+      <c r="B16" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H16" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H16" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="56" t="s">
+      <c r="J16" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L16" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N16" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O16" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P16" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L16" s="56" t="s">
+      <c r="Q16" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R16" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M16" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N16" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P16" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R16" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S16" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>16</v>
       </c>
-      <c r="B17" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>241</v>
+      <c r="B17" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H17" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="56" t="s">
+      <c r="J17" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L17" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P17" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L17" s="56" t="s">
+      <c r="Q17" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R17" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N17" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P17" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q17" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R17" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S17" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>17</v>
       </c>
-      <c r="B18" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>241</v>
+      <c r="B18" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>237</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="H18" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="H18" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I18" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="56" t="s">
+      <c r="J18" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O18" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="P18" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="L18" s="56" t="s">
+      <c r="Q18" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="R18" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M18" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N18" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="P18" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="R18" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S18" s="24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -5975,22 +6425,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D98AB6-DC49-4242-A3C7-7BA04EC48D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A2C078-B6F3-42D9-9295-429D1399C227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -377,12 +377,6 @@
     <t>CTI_Projeto_01</t>
   </si>
   <si>
-    <t>fabricante</t>
-  </si>
-  <si>
-    <t>fornecedor</t>
-  </si>
-  <si>
     <t>código.abnt</t>
   </si>
   <si>
@@ -915,6 +909,12 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>quem.fabricou</t>
+  </si>
+  <si>
+    <t>quem.forneceu</t>
   </si>
 </sst>
 </file>
@@ -1456,15 +1456,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -1531,46 +1523,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
@@ -1630,6 +1582,46 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2177,7 +2169,7 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>94</v>
@@ -2333,7 +2325,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>94</v>
@@ -2345,7 +2337,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46139.499703125002</v>
+        <v>46214.378686921293</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>94</v>
@@ -2389,7 +2381,7 @@
         <v>72</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="44" t="s">
         <v>94</v>
@@ -2400,7 +2392,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>95</v>
@@ -2542,7 +2534,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C2" s="63" t="s">
         <v>84</v>
@@ -2551,10 +2543,10 @@
         <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F2" s="63" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>9</v>
@@ -2588,7 +2580,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>86</v>
@@ -2609,7 +2601,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W2" s="65" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-INC-",A2)</f>
@@ -2634,7 +2626,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C3" s="63" t="s">
         <v>84</v>
@@ -2643,10 +2635,10 @@
         <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F3" s="63" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>9</v>
@@ -2680,7 +2672,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>86</v>
@@ -2701,7 +2693,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W3" s="65" t="str">
         <f t="shared" si="3"/>
@@ -2726,7 +2718,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C4" s="63" t="s">
         <v>84</v>
@@ -2735,10 +2727,10 @@
         <v>85</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F4" s="63" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>9</v>
@@ -2772,7 +2764,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>86</v>
@@ -2793,7 +2785,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W4" s="65" t="str">
         <f t="shared" si="3"/>
@@ -2818,7 +2810,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C5" s="63" t="s">
         <v>84</v>
@@ -2827,10 +2819,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F5" s="63" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>9</v>
@@ -2864,7 +2856,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>86</v>
@@ -2885,7 +2877,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W5" s="65" t="str">
         <f t="shared" si="3"/>
@@ -2910,7 +2902,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C6" s="63" t="s">
         <v>84</v>
@@ -2919,10 +2911,10 @@
         <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F6" s="63" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>9</v>
@@ -2956,7 +2948,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>86</v>
@@ -2977,7 +2969,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W6" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3005,16 +2997,16 @@
         <v>44</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>9</v>
@@ -3040,16 +3032,16 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P7" s="58" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R7" s="34" t="s">
         <v>9</v>
@@ -3067,23 +3059,23 @@
         <v>Sistema Combate</v>
       </c>
       <c r="V7" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W7" s="65" t="str">
         <f t="shared" ref="W7:W28" si="9">CONCATENATE("Key-INC-",A7)</f>
         <v>Key-INC-7</v>
       </c>
       <c r="X7" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="Y7" s="29" t="s">
-        <v>121</v>
-      </c>
       <c r="Z7" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3094,16 +3086,16 @@
         <v>44</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>9</v>
@@ -3129,17 +3121,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O8" s="33" t="str">
         <f t="shared" ref="O8:O21" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
         <v>Alarme</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R8" s="34" t="s">
         <v>9</v>
@@ -3157,23 +3149,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V8" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W8" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-8</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3184,16 +3176,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>9</v>
@@ -3219,17 +3211,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O9" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Campainha</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R9" s="34" t="s">
         <v>9</v>
@@ -3247,23 +3239,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V9" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W9" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Z9" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3274,16 +3266,16 @@
         <v>44</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F10" s="63" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>9</v>
@@ -3309,17 +3301,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O10" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R10" s="34" t="s">
         <v>9</v>
@@ -3337,23 +3329,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V10" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W10" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Z10" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3364,16 +3356,16 @@
         <v>44</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>9</v>
@@ -3399,17 +3391,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O11" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Lumínico</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R11" s="34" t="s">
         <v>9</v>
@@ -3427,23 +3419,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W11" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z11" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3454,16 +3446,16 @@
         <v>44</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F12" s="63" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>9</v>
@@ -3489,17 +3481,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O12" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Caixa Manual</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R12" s="34" t="s">
         <v>9</v>
@@ -3517,23 +3509,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V12" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W12" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Z12" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3544,16 +3536,16 @@
         <v>44</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G13" s="37" t="s">
         <v>9</v>
@@ -3579,17 +3571,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O13" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Detonador</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R13" s="34" t="s">
         <v>9</v>
@@ -3607,23 +3599,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V13" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W13" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Z13" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3634,16 +3626,16 @@
         <v>44</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>9</v>
@@ -3669,17 +3661,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O14" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Sirene</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R14" s="34" t="s">
         <v>9</v>
@@ -3697,23 +3689,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V14" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W14" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3724,16 +3716,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>9</v>
@@ -3759,17 +3751,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O15" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Apito</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R15" s="34" t="s">
         <v>9</v>
@@ -3787,23 +3779,23 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V15" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W15" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Z15" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3814,16 +3806,16 @@
         <v>44</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F16" s="63" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>9</v>
@@ -3849,17 +3841,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O16" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Terminal Combate Fogo</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="R16" s="34" t="s">
         <v>9</v>
@@ -3877,23 +3869,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V16" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W16" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Z16" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3904,16 +3896,16 @@
         <v>44</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F17" s="63" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>9</v>
@@ -3939,17 +3931,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O17" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Entrada</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="R17" s="34" t="s">
         <v>9</v>
@@ -3967,23 +3959,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V17" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W17" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Z17" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3994,16 +3986,16 @@
         <v>44</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F18" s="63" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>9</v>
@@ -4029,17 +4021,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O18" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Carretel</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R18" s="34" t="s">
         <v>9</v>
@@ -4057,23 +4049,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W18" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Z18" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -4084,16 +4076,16 @@
         <v>44</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>9</v>
@@ -4119,17 +4111,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O19" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Canhão</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R19" s="34" t="s">
         <v>9</v>
@@ -4147,23 +4139,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V19" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W19" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Z19" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -4174,16 +4166,16 @@
         <v>44</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G20" s="37" t="s">
         <v>9</v>
@@ -4209,17 +4201,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O20" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Hidrante</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R20" s="34" t="s">
         <v>9</v>
@@ -4237,23 +4229,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V20" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W20" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-20</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Z20" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -4264,16 +4256,16 @@
         <v>44</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F21" s="63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>9</v>
@@ -4299,17 +4291,17 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O21" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Sprinkler</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R21" s="34" t="s">
         <v>9</v>
@@ -4327,23 +4319,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V21" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W21" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-21</v>
       </c>
       <c r="X21" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Z21" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -4354,16 +4346,16 @@
         <v>44</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F22" s="63" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>9</v>
@@ -4389,16 +4381,16 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O22" s="29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R22" s="34" t="s">
         <v>9</v>
@@ -4416,23 +4408,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V22" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W22" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-22</v>
       </c>
       <c r="X22" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z22" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4443,16 +4435,16 @@
         <v>44</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>9</v>
@@ -4478,13 +4470,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O23" s="58" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P23" s="58" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q23" s="30" t="str">
         <f t="shared" ref="Q23" si="12">_xlfn.TRANSLATE(P23,"pt","es")</f>
@@ -4506,23 +4498,23 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V23" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W23" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-23</v>
       </c>
       <c r="X23" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y23" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="Y23" s="29" t="s">
-        <v>184</v>
-      </c>
       <c r="Z23" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4533,16 +4525,16 @@
         <v>44</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>9</v>
@@ -4568,13 +4560,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f>_xlfn.TRANSLATE(P24,"pt","es")</f>
@@ -4596,23 +4588,23 @@
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V24" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W24" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z24" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4623,16 +4615,16 @@
         <v>44</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>9</v>
@@ -4658,13 +4650,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O25" s="58" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P25" s="58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f t="shared" ref="Q25:Q27" si="16">_xlfn.TRANSLATE(P25,"pt","es")</f>
@@ -4686,23 +4678,23 @@
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V25" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W25" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z25" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4713,16 +4705,16 @@
         <v>44</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="F26" s="47" t="s">
         <v>130</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>132</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>9</v>
@@ -4748,13 +4740,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O26" s="58" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P26" s="58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="30" t="str">
         <f t="shared" si="16"/>
@@ -4776,23 +4768,23 @@
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V26" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W26" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z26" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4803,16 +4795,16 @@
         <v>44</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>9</v>
@@ -4838,13 +4830,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O27" s="58" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P27" s="58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="30" t="str">
         <f t="shared" si="16"/>
@@ -4866,23 +4858,23 @@
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V27" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W27" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Z27" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4893,16 +4885,16 @@
         <v>44</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G28" s="37" t="s">
         <v>9</v>
@@ -4928,13 +4920,13 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N28" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P28" s="58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" ref="Q28" si="19">_xlfn.TRANSLATE(P28,"pt","es")</f>
@@ -4956,23 +4948,23 @@
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V28" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W28" s="65" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Z28" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4980,67 +4972,60 @@
     <sortCondition ref="F7:F895"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA7">
-    <cfRule type="cellIs" dxfId="26" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:A28">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1502"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F22">
-    <cfRule type="duplicateValues" dxfId="24" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="23" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1474"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O17:O22 A1:D1 F1:O1 Q1:X1 Z1:AA1 S7:S28 E8:F16 L8:O16 B8:B22 Q8:Q22 X8:Y22 AA8:XFD22 F17:F22 L17:M22 E17:E23 N17:N23">
-    <cfRule type="cellIs" dxfId="18" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="66" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22">
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23:O28">
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7">
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA7">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA23:AA28">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A28">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5255,7 +5240,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5282,9 +5267,9 @@
     <col min="7" max="7" width="56.3828125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.3046875" customWidth="1"/>
     <col min="9" max="9" width="19.3828125" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3046875" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.4609375" customWidth="1"/>
     <col min="14" max="15" width="6.4609375" customWidth="1"/>
     <col min="16" max="16" width="5.3828125" customWidth="1"/>
@@ -5360,7 +5345,7 @@
         <v>100</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>9</v>
@@ -5372,7 +5357,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H2" s="55" t="s">
         <v>9</v>
@@ -5416,10 +5401,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>83</v>
@@ -5431,13 +5416,13 @@
         <v>78</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H3" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J3" s="55" t="s">
         <v>9</v>
@@ -5467,7 +5452,7 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5475,10 +5460,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D4" s="56" t="s">
         <v>83</v>
@@ -5490,13 +5475,13 @@
         <v>78</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H4" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J4" s="55" t="s">
         <v>9</v>
@@ -5526,7 +5511,7 @@
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5534,58 +5519,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K5" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="H5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="55" t="s">
+      <c r="L5" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N5" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M5" s="24" t="s">
+      <c r="O5" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P5" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="R5" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N5" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P5" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="R5" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5593,22 +5578,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H6" s="55" t="s">
         <v>9</v>
@@ -5617,34 +5602,34 @@
         <v>9</v>
       </c>
       <c r="J6" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M6" s="24" t="s">
+      <c r="O6" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="R6" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N6" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P6" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="R6" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S6" s="24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5652,22 +5637,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H7" s="55" t="s">
         <v>9</v>
@@ -5676,34 +5661,34 @@
         <v>9</v>
       </c>
       <c r="J7" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M7" s="24" t="s">
+      <c r="O7" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P7" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R7" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P7" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R7" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S7" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5711,22 +5696,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>9</v>
@@ -5735,34 +5720,34 @@
         <v>9</v>
       </c>
       <c r="J8" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L8" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L8" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M8" s="24" t="s">
+      <c r="O8" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R8" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N8" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P8" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R8" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S8" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5770,22 +5755,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H9" s="55" t="s">
         <v>9</v>
@@ -5794,34 +5779,34 @@
         <v>9</v>
       </c>
       <c r="J9" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L9" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L9" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" s="24" t="s">
+      <c r="O9" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R9" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P9" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q9" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R9" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S9" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5829,22 +5814,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H10" s="55" t="s">
         <v>9</v>
@@ -5853,34 +5838,34 @@
         <v>9</v>
       </c>
       <c r="J10" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L10" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L10" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M10" s="24" t="s">
+      <c r="O10" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R10" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P10" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R10" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S10" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5888,22 +5873,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H11" s="55" t="s">
         <v>9</v>
@@ -5912,34 +5897,34 @@
         <v>9</v>
       </c>
       <c r="J11" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L11" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L11" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M11" s="24" t="s">
+      <c r="O11" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R11" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P11" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q11" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R11" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S11" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5947,22 +5932,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H12" s="55" t="s">
         <v>9</v>
@@ -5971,34 +5956,34 @@
         <v>9</v>
       </c>
       <c r="J12" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L12" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L12" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M12" s="24" t="s">
+      <c r="O12" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P12" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R12" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N12" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P12" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R12" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S12" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6006,22 +5991,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H13" s="55" t="s">
         <v>9</v>
@@ -6030,34 +6015,34 @@
         <v>9</v>
       </c>
       <c r="J13" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L13" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L13" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M13" s="24" t="s">
+      <c r="O13" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P13" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R13" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N13" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P13" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q13" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R13" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6065,22 +6050,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H14" s="55" t="s">
         <v>9</v>
@@ -6089,34 +6074,34 @@
         <v>9</v>
       </c>
       <c r="J14" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L14" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L14" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M14" s="24" t="s">
+      <c r="O14" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P14" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R14" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N14" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P14" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R14" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S14" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6124,22 +6109,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H15" s="55" t="s">
         <v>9</v>
@@ -6148,34 +6133,34 @@
         <v>9</v>
       </c>
       <c r="J15" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N15" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M15" s="24" t="s">
+      <c r="O15" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R15" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P15" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R15" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S15" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6183,22 +6168,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H16" s="55" t="s">
         <v>9</v>
@@ -6207,34 +6192,34 @@
         <v>9</v>
       </c>
       <c r="J16" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L16" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N16" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M16" s="24" t="s">
+      <c r="O16" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P16" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R16" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N16" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P16" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R16" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S16" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6242,22 +6227,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="38" t="s">
         <v>235</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>237</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H17" s="55" t="s">
         <v>9</v>
@@ -6266,34 +6251,34 @@
         <v>9</v>
       </c>
       <c r="J17" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L17" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N17" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="24" t="s">
+      <c r="O17" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P17" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R17" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N17" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P17" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q17" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R17" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S17" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -6301,22 +6286,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H18" s="55" t="s">
         <v>9</v>
@@ -6325,34 +6310,34 @@
         <v>9</v>
       </c>
       <c r="J18" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="L18" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M18" s="24" t="s">
+      <c r="O18" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R18" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N18" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="P18" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="R18" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S18" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6425,22 +6410,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A2C078-B6F3-42D9-9295-429D1399C227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD0A68A-9157-4E49-A0DA-9CB57B6BD9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="280">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -203,9 +203,6 @@
     <t>000 Traducción Classe 5</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -872,18 +869,9 @@
     <t>Reserva.Intermediária</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
@@ -915,6 +903,15 @@
   </si>
   <si>
     <t>quem.forneceu</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1356,18 +1353,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1392,9 +1377,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1406,9 +1388,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1452,11 +1431,76 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2134,280 +2178,280 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="40.07421875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="62"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="B2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="41" t="s">
+      <c r="B8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46214.378686921293</v>
-      </c>
-      <c r="C18" s="44" t="s">
+        <v>46216.38966828704</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Fire Fighting Objects</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>96</v>
+      <c r="C24" s="40" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2419,153 +2463,154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.4609375" customWidth="1"/>
-    <col min="4" max="4" width="7.07421875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
-    <col min="6" max="6" width="10.765625" style="46" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="36" customWidth="1"/>
-    <col min="12" max="12" width="7.4609375" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="9.61328125" customWidth="1"/>
-    <col min="15" max="15" width="14.84375" customWidth="1"/>
-    <col min="16" max="16" width="49.53515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.53515625" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.61328125" customWidth="1"/>
-    <col min="20" max="20" width="7.23046875" customWidth="1"/>
-    <col min="21" max="21" width="10.69140625" customWidth="1"/>
-    <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.15234375" style="60" customWidth="1"/>
-    <col min="24" max="24" width="53.07421875" style="60" customWidth="1"/>
-    <col min="25" max="25" width="22.07421875" style="61" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
-    <col min="27" max="27" width="44.69140625" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="54" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="68.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.140625" style="55" customWidth="1"/>
+    <col min="26" max="26" width="5.5703125" style="54" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="50" t="s">
+      <c r="M1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60">
         <v>2</v>
       </c>
-      <c r="J1" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="S1" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z1" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA1" s="40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="32">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C2" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="63" t="s">
-        <v>269</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="37" t="s">
+      <c r="E2" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2573,37 +2618,37 @@
       </c>
       <c r="N2" s="33" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="30" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="35" t="str">
+      <c r="U2" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W2" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W2" s="59" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
@@ -2613,51 +2658,51 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="34" t="s">
-        <v>9</v>
+      <c r="Z2" s="30" t="s">
+        <v>279</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C3" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>271</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="37" t="s">
+      <c r="E3" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>267</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2665,37 +2710,37 @@
       </c>
       <c r="N3" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="35" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W3" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-3</v>
       </c>
@@ -2705,7 +2750,7 @@
       <c r="Y3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="34" t="s">
+      <c r="Z3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="30" t="str">
@@ -2713,43 +2758,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F4" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="37" t="s">
+      <c r="E4" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2757,37 +2802,37 @@
       </c>
       <c r="N4" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="35" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W4" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W4" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-4</v>
       </c>
@@ -2797,7 +2842,7 @@
       <c r="Y4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="34" t="s">
+      <c r="Z4" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="30" t="str">
@@ -2805,43 +2850,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F5" s="63" t="s">
-        <v>275</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="37" t="s">
+      <c r="E5" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2849,37 +2894,37 @@
       </c>
       <c r="N5" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="35" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W5" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W5" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-5</v>
       </c>
@@ -2889,7 +2934,7 @@
       <c r="Y5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="34" t="s">
+      <c r="Z5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="30" t="str">
@@ -2897,43 +2942,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F6" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="37" t="s">
+      <c r="E6" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2941,37 +2986,37 @@
       </c>
       <c r="N6" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="35" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W6" s="65" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W6" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-6</v>
       </c>
@@ -2981,7 +3026,7 @@
       <c r="Y6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="34" t="s">
+      <c r="Z6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="30" t="str">
@@ -2989,38 +3034,38 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32">
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="E7" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="F7" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
@@ -3032,84 +3077,84 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="P7" s="58" t="s">
+        <v>251</v>
+      </c>
+      <c r="P7" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q7" s="52" t="s">
         <v>259</v>
       </c>
-      <c r="Q7" s="58" t="s">
-        <v>260</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="35" t="str">
+      <c r="R7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="30" t="str">
         <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
-      <c r="T7" s="35" t="str">
+      <c r="T7" s="30" t="str">
         <f t="shared" ref="T7:U20" si="8">SUBSTITUTE(D7, ".", " ")</f>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U7" s="35" t="str">
+      <c r="U7" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema Combate</v>
       </c>
-      <c r="V7" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W7" s="65" t="str">
+      <c r="V7" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W7" s="59" t="str">
         <f t="shared" ref="W7:W28" si="9">CONCATENATE("Key-INC-",A7)</f>
         <v>Key-INC-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z7" s="34" t="s">
-        <v>257</v>
+        <v>118</v>
+      </c>
+      <c r="Z7" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA7" s="30" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="60">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="37" t="s">
+      <c r="F8" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
@@ -3121,85 +3166,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O8" s="33" t="str">
         <f t="shared" ref="O8:O21" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
         <v>Alarme</v>
       </c>
       <c r="P8" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="Q8" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="35" t="str">
+      <c r="R8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T8" s="35" t="str">
+      <c r="T8" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U8" s="35" t="str">
+      <c r="U8" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V8" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W8" s="65" t="str">
+      <c r="V8" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W8" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-8</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>257</v>
+        <v>185</v>
+      </c>
+      <c r="Z8" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="32">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="60">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
@@ -3211,85 +3256,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O9" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Campainha</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="Q9" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="35" t="str">
+      <c r="R9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T9" s="35" t="str">
+      <c r="T9" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U9" s="35" t="str">
+      <c r="U9" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V9" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W9" s="65" t="str">
+      <c r="V9" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W9" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>257</v>
+        <v>186</v>
+      </c>
+      <c r="Z9" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
@@ -3301,85 +3346,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O10" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P10" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="Q10" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="35" t="str">
+      <c r="R10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T10" s="35" t="str">
+      <c r="T10" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U10" s="35" t="str">
+      <c r="U10" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V10" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W10" s="65" t="str">
+      <c r="V10" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W10" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>257</v>
+        <v>187</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="32">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F11" s="63" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
@@ -3391,85 +3436,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O11" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Lumínico</v>
       </c>
       <c r="P11" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q11" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="Q11" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="35" t="str">
+      <c r="R11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T11" s="35" t="str">
+      <c r="T11" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U11" s="35" t="str">
+      <c r="U11" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V11" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W11" s="65" t="str">
+      <c r="V11" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W11" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z11" s="34" t="s">
-        <v>257</v>
+        <v>188</v>
+      </c>
+      <c r="Z11" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
@@ -3481,85 +3526,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O12" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Caixa Manual</v>
       </c>
       <c r="P12" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="Q12" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="R12" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="35" t="str">
+      <c r="R12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T12" s="35" t="str">
+      <c r="T12" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U12" s="35" t="str">
+      <c r="U12" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V12" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W12" s="65" t="str">
+      <c r="V12" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W12" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>257</v>
+        <v>189</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" s="63" t="s">
-        <v>148</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
@@ -3571,85 +3616,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O13" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Detonador</v>
       </c>
       <c r="P13" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q13" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="Q13" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="R13" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="35" t="str">
+      <c r="R13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T13" s="35" t="str">
+      <c r="T13" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U13" s="35" t="str">
+      <c r="U13" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V13" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W13" s="65" t="str">
+      <c r="V13" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W13" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>257</v>
+        <v>190</v>
+      </c>
+      <c r="Z13" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
@@ -3661,85 +3706,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O14" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Sirene</v>
       </c>
       <c r="P14" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q14" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="Q14" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="R14" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="35" t="str">
+      <c r="R14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T14" s="35" t="str">
+      <c r="T14" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U14" s="35" t="str">
+      <c r="U14" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V14" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W14" s="65" t="str">
+      <c r="V14" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W14" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z14" s="34" t="s">
-        <v>257</v>
+        <v>191</v>
+      </c>
+      <c r="Z14" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
@@ -3751,85 +3796,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O15" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Alarme Apito</v>
       </c>
       <c r="P15" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q15" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="Q15" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="R15" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="35" t="str">
+      <c r="R15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T15" s="35" t="str">
+      <c r="T15" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U15" s="35" t="str">
+      <c r="U15" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V15" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W15" s="65" t="str">
+      <c r="V15" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W15" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z15" s="34" t="s">
-        <v>257</v>
+        <v>192</v>
+      </c>
+      <c r="Z15" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
@@ -3841,85 +3886,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O16" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Terminal Combate Fogo</v>
       </c>
       <c r="P16" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q16" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="Q16" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="R16" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="35" t="str">
+      <c r="R16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T16" s="35" t="str">
+      <c r="T16" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U16" s="35" t="str">
+      <c r="U16" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V16" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W16" s="65" t="str">
+      <c r="V16" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W16" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z16" s="34" t="s">
-        <v>257</v>
+        <v>181</v>
+      </c>
+      <c r="Z16" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
@@ -3931,85 +3976,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O17" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Entrada</v>
       </c>
       <c r="P17" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q17" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="Q17" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="R17" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="35" t="str">
+      <c r="R17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T17" s="35" t="str">
+      <c r="T17" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U17" s="35" t="str">
+      <c r="U17" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V17" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W17" s="65" t="str">
+      <c r="V17" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W17" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z17" s="34" t="s">
-        <v>257</v>
+        <v>193</v>
+      </c>
+      <c r="Z17" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
@@ -4021,85 +4066,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O18" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Carretel</v>
       </c>
       <c r="P18" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q18" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Q18" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="R18" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="35" t="str">
+      <c r="R18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T18" s="35" t="str">
+      <c r="T18" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U18" s="35" t="str">
+      <c r="U18" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V18" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W18" s="65" t="str">
+      <c r="V18" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W18" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z18" s="34" t="s">
-        <v>257</v>
+        <v>194</v>
+      </c>
+      <c r="Z18" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="32">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
@@ -4111,85 +4156,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O19" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Mangueira Canhão</v>
       </c>
       <c r="P19" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q19" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="Q19" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="R19" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="35" t="str">
+      <c r="R19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T19" s="35" t="str">
+      <c r="T19" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U19" s="35" t="str">
+      <c r="U19" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V19" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W19" s="65" t="str">
+      <c r="V19" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W19" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="Z19" s="34" t="s">
-        <v>257</v>
+        <v>195</v>
+      </c>
+      <c r="Z19" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="32">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
@@ -4201,85 +4246,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O20" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Hidrante</v>
       </c>
       <c r="P20" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="Q20" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="R20" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="35" t="str">
+      <c r="R20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T20" s="35" t="str">
+      <c r="T20" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U20" s="35" t="str">
+      <c r="U20" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V20" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W20" s="65" t="str">
+      <c r="V20" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W20" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-20</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z20" s="34" t="s">
-        <v>257</v>
+        <v>196</v>
+      </c>
+      <c r="Z20" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="32">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F21" s="63" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
@@ -4291,85 +4336,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O21" s="33" t="str">
         <f t="shared" si="11"/>
         <v>Sprinkler</v>
       </c>
       <c r="P21" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q21" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="Q21" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="R21" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="35" t="str">
+      <c r="R21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T21" s="35" t="str">
+      <c r="T21" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U21" s="35" t="str">
+      <c r="U21" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V21" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W21" s="65" t="str">
+      <c r="V21" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W21" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-21</v>
       </c>
       <c r="X21" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z21" s="34" t="s">
-        <v>257</v>
+        <v>197</v>
+      </c>
+      <c r="Z21" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>174</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
@@ -4381,84 +4426,84 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O22" s="29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P22" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q22" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Q22" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="R22" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="35" t="str">
+      <c r="R22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T22" s="35" t="str">
+      <c r="T22" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U22" s="35" t="str">
+      <c r="U22" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V22" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W22" s="65" t="str">
+      <c r="V22" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W22" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-22</v>
       </c>
       <c r="X22" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z22" s="34" t="s">
-        <v>257</v>
+        <v>198</v>
+      </c>
+      <c r="Z22" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
@@ -4470,85 +4515,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="O23" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="P23" s="58" t="s">
-        <v>118</v>
+        <v>254</v>
+      </c>
+      <c r="O23" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="P23" s="52" t="s">
+        <v>117</v>
       </c>
       <c r="Q23" s="30" t="str">
         <f t="shared" ref="Q23" si="12">_xlfn.TRANSLATE(P23,"pt","es")</f>
         <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
       </c>
-      <c r="R23" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="35" t="str">
+      <c r="R23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="30" t="str">
         <f t="shared" ref="S23:U28" si="13">SUBSTITUTE(C23, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
-      <c r="T23" s="35" t="str">
+      <c r="T23" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U23" s="35" t="str">
+      <c r="U23" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V23" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W23" s="65" t="str">
+      <c r="V23" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W23" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-23</v>
       </c>
       <c r="X23" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z23" s="34" t="s">
-        <v>257</v>
+        <v>181</v>
+      </c>
+      <c r="Z23" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F24" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="E24" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="37" t="s">
+      <c r="G24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
@@ -4560,85 +4605,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O24" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="P24" s="58" t="s">
-        <v>110</v>
+        <v>255</v>
+      </c>
+      <c r="O24" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="P24" s="52" t="s">
+        <v>109</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f>_xlfn.TRANSLATE(P24,"pt","es")</f>
         <v>Cisterna Superior</v>
       </c>
-      <c r="R24" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="35" t="str">
+      <c r="R24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T24" s="35" t="str">
+      <c r="T24" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U24" s="35" t="str">
+      <c r="U24" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V24" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W24" s="65" t="str">
+      <c r="V24" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W24" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z24" s="34" t="s">
-        <v>257</v>
+        <v>114</v>
+      </c>
+      <c r="Z24" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F25" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="F25" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="37" t="s">
+      <c r="G25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
@@ -4650,85 +4695,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O25" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="P25" s="58" t="s">
-        <v>113</v>
+        <v>255</v>
+      </c>
+      <c r="O25" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="P25" s="52" t="s">
+        <v>112</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f t="shared" ref="Q25:Q27" si="16">_xlfn.TRANSLATE(P25,"pt","es")</f>
         <v>Cisterna intermedia</v>
       </c>
-      <c r="R25" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="35" t="str">
+      <c r="R25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T25" s="35" t="str">
+      <c r="T25" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U25" s="35" t="str">
+      <c r="U25" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V25" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W25" s="65" t="str">
+      <c r="V25" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W25" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z25" s="34" t="s">
-        <v>257</v>
+        <v>114</v>
+      </c>
+      <c r="Z25" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
@@ -4740,85 +4785,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O26" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="P26" s="58" t="s">
-        <v>111</v>
+        <v>255</v>
+      </c>
+      <c r="O26" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="P26" s="52" t="s">
+        <v>110</v>
       </c>
       <c r="Q26" s="30" t="str">
         <f t="shared" si="16"/>
         <v>Cisterna Inferior</v>
       </c>
-      <c r="R26" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="35" t="str">
+      <c r="R26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T26" s="35" t="str">
+      <c r="T26" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U26" s="35" t="str">
+      <c r="U26" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V26" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W26" s="65" t="str">
+      <c r="V26" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W26" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z26" s="34" t="s">
-        <v>257</v>
+        <v>114</v>
+      </c>
+      <c r="Z26" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L27" s="33" t="str">
@@ -4830,85 +4875,85 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O27" s="58" t="s">
-        <v>249</v>
-      </c>
-      <c r="P27" s="58" t="s">
-        <v>112</v>
+        <v>255</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>111</v>
       </c>
       <c r="Q27" s="30" t="str">
         <f t="shared" si="16"/>
         <v>Tubería de agua fría</v>
       </c>
-      <c r="R27" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="35" t="str">
+      <c r="R27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema Predial</v>
       </c>
-      <c r="T27" s="35" t="str">
+      <c r="T27" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U27" s="35" t="str">
+      <c r="U27" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V27" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W27" s="65" t="str">
+      <c r="V27" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W27" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z27" s="34" t="s">
-        <v>257</v>
+        <v>104</v>
+      </c>
+      <c r="Z27" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>109</v>
+        <v>277</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
@@ -4920,51 +4965,51 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N28" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O28" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="P28" s="58" t="s">
-        <v>112</v>
+        <v>255</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>111</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" ref="Q28" si="19">_xlfn.TRANSLATE(P28,"pt","es")</f>
         <v>Tubería de agua fría</v>
       </c>
-      <c r="R28" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="35" t="str">
+      <c r="R28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="30" t="str">
         <f t="shared" ref="S28" si="20">SUBSTITUTE(C28, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
-      <c r="T28" s="35" t="str">
+      <c r="T28" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sis Incêndio</v>
       </c>
-      <c r="U28" s="35" t="str">
+      <c r="U28" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V28" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W28" s="65" t="str">
+      <c r="V28" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="W28" s="59" t="str">
         <f t="shared" si="9"/>
         <v>Key-INC-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z28" s="34" t="s">
-        <v>257</v>
+        <v>104</v>
+      </c>
+      <c r="Z28" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4972,58 +5017,63 @@
     <sortCondition ref="F7:F895"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A28">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1502"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F22">
-    <cfRule type="duplicateValues" dxfId="19" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="18" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1474"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1501"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O17:O22 A1:D1 F1:O1 Q1:X1 Z1:AA1 S7:S28 E8:F16 L8:O16 B8:B22 Q8:Q22 X8:Y22 AA8:XFD22 F17:F22 L17:M22 E17:E23 N17:N23">
-    <cfRule type="cellIs" dxfId="13" priority="66" operator="equal">
+  <conditionalFormatting sqref="O17:O22 A1:D1 F1:O1 Q1:X1 Z1:AA1 S7:S28 E8:F16 L8:O16 Q8:Q22 X8:Y22 AA8:XFD22 F17:F22 L17:M22 E17:E23 N17:N23">
+    <cfRule type="cellIs" dxfId="19" priority="72" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23:O28">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7">
-    <cfRule type="duplicateValues" dxfId="10" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA7">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA7">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA23:AA28">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="25" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B28">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5035,15 +5085,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5108,7 +5158,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5173,7 +5223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5240,7 +5290,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5256,1088 +5306,1089 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.85" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69140625" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" customWidth="1"/>
-    <col min="4" max="4" width="7.07421875" customWidth="1"/>
-    <col min="5" max="5" width="7.4609375" customWidth="1"/>
-    <col min="6" max="6" width="4.61328125" customWidth="1"/>
-    <col min="7" max="7" width="56.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.3046875" customWidth="1"/>
-    <col min="9" max="9" width="19.3828125" customWidth="1"/>
-    <col min="10" max="10" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.4609375" customWidth="1"/>
-    <col min="14" max="15" width="6.4609375" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
-    <col min="17" max="17" width="18.15234375" customWidth="1"/>
-    <col min="18" max="18" width="6.765625" customWidth="1"/>
-    <col min="19" max="19" width="18.3046875" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>77</v>
-      </c>
       <c r="I1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="H2" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="55" t="s">
+      <c r="L2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="55" t="s">
+      <c r="P2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="55" t="s">
+      <c r="R2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="H3" s="55" t="s">
-        <v>78</v>
+      <c r="H3" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="J3" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="J3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>100</v>
+        <v>234</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="H4" s="55" t="s">
-        <v>78</v>
+        <v>219</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="J4" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="J4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="55" t="s">
+      <c r="N4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="55" t="s">
+      <c r="P4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="55" t="s">
+      <c r="R4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>219</v>
+      <c r="B5" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="H5" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="55" t="s">
-        <v>279</v>
+      <c r="J5" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L5" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M5" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P5" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N5" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P5" s="55" t="s">
+      <c r="Q5" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="R5" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q5" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="R5" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>235</v>
+      <c r="B6" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="K6" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>280</v>
+      <c r="L6" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P6" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N6" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P6" s="55" t="s">
+      <c r="Q6" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="R6" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q6" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="R6" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S6" s="24" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>219</v>
+      <c r="B7" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H7" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="H7" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="55" t="s">
-        <v>279</v>
+      <c r="J7" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L7" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M7" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P7" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N7" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P7" s="55" t="s">
+      <c r="Q7" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q7" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R7" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S7" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="53" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>219</v>
+      <c r="B8" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H8" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="55" t="s">
-        <v>279</v>
+      <c r="J8" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L8" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M8" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P8" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N8" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P8" s="55" t="s">
+      <c r="Q8" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R8" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R8" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S8" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="L9" s="49" t="s">
+        <v>276</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P9" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="47" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L9" s="55" t="s">
-        <v>280</v>
-      </c>
-      <c r="M9" s="24" t="s">
+      <c r="C10" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="L10" s="49" t="s">
+        <v>276</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P10" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N9" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P9" s="55" t="s">
+      <c r="Q10" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R10" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q9" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R9" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H10" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L10" s="55" t="s">
-        <v>280</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="N10" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R10" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S10" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>219</v>
+      <c r="B11" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H11" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="55" t="s">
-        <v>279</v>
+      <c r="J11" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L11" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M11" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P11" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N11" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P11" s="55" t="s">
+      <c r="Q11" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R11" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q11" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R11" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S11" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>219</v>
+      <c r="B12" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H12" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="H12" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="55" t="s">
-        <v>279</v>
+      <c r="J12" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L12" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L12" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P12" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N12" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P12" s="55" t="s">
+      <c r="Q12" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q12" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R12" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S12" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>12</v>
       </c>
-      <c r="B13" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>235</v>
+      <c r="B13" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H13" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H13" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="55" t="s">
-        <v>279</v>
+      <c r="J13" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L13" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L13" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M13" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P13" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P13" s="55" t="s">
+      <c r="Q13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R13" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q13" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R13" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>13</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>235</v>
+      <c r="B14" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H14" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H14" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J14" s="55" t="s">
-        <v>279</v>
+      <c r="J14" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L14" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L14" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M14" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P14" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N14" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P14" s="55" t="s">
+      <c r="Q14" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R14" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q14" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R14" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S14" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>14</v>
       </c>
-      <c r="B15" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>235</v>
+      <c r="B15" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H15" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H15" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J15" s="55" t="s">
-        <v>279</v>
+      <c r="J15" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L15" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L15" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M15" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O15" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P15" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P15" s="55" t="s">
+      <c r="Q15" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R15" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q15" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R15" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S15" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>15</v>
       </c>
-      <c r="B16" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>235</v>
+      <c r="B16" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H16" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H16" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="55" t="s">
-        <v>279</v>
+      <c r="J16" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M16" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N16" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O16" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P16" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N16" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P16" s="55" t="s">
+      <c r="Q16" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R16" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q16" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R16" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S16" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>16</v>
       </c>
-      <c r="B17" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>235</v>
+      <c r="B17" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H17" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H17" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="55" t="s">
-        <v>279</v>
+      <c r="J17" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L17" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M17" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N17" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P17" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N17" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P17" s="55" t="s">
+      <c r="Q17" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R17" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q17" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R17" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S17" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>17</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>235</v>
-      </c>
       <c r="F18" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H18" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="H18" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I18" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="55" t="s">
-        <v>279</v>
+      <c r="J18" s="49" t="s">
+        <v>275</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="L18" s="55" t="s">
-        <v>280</v>
+        <v>239</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>276</v>
       </c>
       <c r="M18" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="P18" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N18" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="P18" s="55" t="s">
+      <c r="Q18" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R18" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q18" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="R18" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S18" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -6350,38 +6401,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.921875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.23046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6410,22 +6461,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD0A68A-9157-4E49-A0DA-9CB57B6BD9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A201C1EB-F585-4887-A7A4-57930AECCDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
     <sheet name="Classes" sheetId="17" r:id="rId2"/>
     <sheet name="Disjunt" sheetId="3" r:id="rId3"/>
-    <sheet name="FatosIn" sheetId="25" r:id="rId4"/>
-    <sheet name="Interop" sheetId="16" r:id="rId5"/>
+    <sheet name="Interop" sheetId="16" r:id="rId4"/>
+    <sheet name="FatosIn" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!#REF!</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="319">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -386,12 +386,6 @@
     <t>categoria.revit</t>
   </si>
   <si>
-    <t>[ IfcPipeSegment , IfcPipeFitting ]</t>
-  </si>
-  <si>
-    <t>[ OST_PipingSystem , OST_PipeSegments , OST_PipeFitting , OST_PipeCurves , OST_PipeConnections , OST_PipeFittingInsulation ]</t>
-  </si>
-  <si>
     <t>é.pertencente.a</t>
   </si>
   <si>
@@ -413,15 +407,9 @@
     <t>Cisterna Intermediária</t>
   </si>
   <si>
-    <t>Instalações</t>
-  </si>
-  <si>
     <t>[ IfcTank ]</t>
   </si>
   <si>
-    <t>"[ IfcPipeSegment , IfcPipeFitting ]"</t>
-  </si>
-  <si>
     <t>[ OST_PipingSystem ]</t>
   </si>
   <si>
@@ -434,9 +422,6 @@
     <t>"[ OST_PipingSystem ]"</t>
   </si>
   <si>
-    <t>"[ OST_PipeSegments , OST_PipeFitting ]"</t>
-  </si>
-  <si>
     <t>Objetos_de_Combate_Incêndio</t>
   </si>
   <si>
@@ -623,12 +608,6 @@
     <t>Tubulação.Mangueira</t>
   </si>
   <si>
-    <t>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</t>
-  </si>
-  <si>
-    <t>Alarm of Light.</t>
-  </si>
-  <si>
     <t>[ IfcAlarm ]</t>
   </si>
   <si>
@@ -671,63 +650,6 @@
     <t>[ IfcFireSuppressionTerminalSPRINKLERDEFLECTOR ]</t>
   </si>
   <si>
-    <t>Device that signals the existence of a condition or situation of danger.</t>
-  </si>
-  <si>
-    <t>Audible alarm.</t>
-  </si>
-  <si>
-    <t>Alarm activation mechanism in which activation occurs by a pulling action.</t>
-  </si>
-  <si>
-    <t>A coin-sized device that is used as a high warning signal to train train drivers.</t>
-  </si>
-  <si>
-    <t>Audible alarm produced by a siren.</t>
-  </si>
-  <si>
-    <t>Audible alarm produced by a whistle.</t>
-  </si>
-  <si>
-    <t>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</t>
-  </si>
-  <si>
-    <t>Symmetrical pipe connection that joins two or more inlets into a single pipe.</t>
-  </si>
-  <si>
-    <t>Support structure on which a hose can be wound.</t>
-  </si>
-  <si>
-    <t>Fire monitor.</t>
-  </si>
-  <si>
-    <t>A device, installed in a pipe, through which a temporary supply of water can be supplied.</t>
-  </si>
-  <si>
-    <t>A device for spraying water from a pipe under pressure over an area.</t>
-  </si>
-  <si>
-    <t>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire suppression Pipe to feed Sprinkler </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire suppression Pipe to feed Hidrants </t>
-  </si>
-  <si>
-    <t>Upper Reserve Fire Cistern</t>
-  </si>
-  <si>
-    <t>Intermediate Reserve Fire Cistern</t>
-  </si>
-  <si>
-    <t>Lower Reserve Fire Cistern</t>
-  </si>
-  <si>
-    <t>Fire suppression system accessory like brackets, hooks, pedestals, etc.</t>
-  </si>
-  <si>
     <t>Sis_INC_01</t>
   </si>
   <si>
@@ -740,57 +662,9 @@
     <t>SPK_ID_453909</t>
   </si>
   <si>
-    <t>TuboInc_ID_678250</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678251</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678252</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678253</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678254</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678255</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678256</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678257</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678258</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678259</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678260</t>
-  </si>
-  <si>
-    <t>TuboInc_ID_678261</t>
-  </si>
-  <si>
     <t>Sis_INC_02</t>
   </si>
   <si>
-    <t>"Instância de Tubulação que pertence ao sistema INC01 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
-  </si>
-  <si>
-    <t>"Instância de Tubulação que pertence ao sistema INC02 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
-  </si>
-  <si>
-    <t>"Instância de Sprinkler que pertence ao sistema INC01 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
-  </si>
-  <si>
-    <t>"Instância de Sprinkler que pertence ao sistema INC02 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
-  </si>
-  <si>
     <t>"Nome da empresa fabricante do produto."</t>
   </si>
   <si>
@@ -845,18 +719,12 @@
     <t>[ 3E.62 ]</t>
   </si>
   <si>
-    <t>"[ 3E.62 ]"</t>
-  </si>
-  <si>
     <t>Sistema de Combate a Incêndio Predial</t>
   </si>
   <si>
     <t>Sistema de Combate a Incendio Predial</t>
   </si>
   <si>
-    <t>Building Fire Protection System</t>
-  </si>
-  <si>
     <t>Alarmes.de.Incêndio</t>
   </si>
   <si>
@@ -912,6 +780,255 @@
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Detetor.de.Fumaça</t>
+  </si>
+  <si>
+    <t>Detetor de fumação.</t>
+  </si>
+  <si>
+    <t>Detector de humo.</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.Incêndio</t>
+  </si>
+  <si>
+    <t>Porta corta-fogo que fechada impede a passagem de fogo e fumaça.</t>
+  </si>
+  <si>
+    <t>[ OST_Doors ]</t>
+  </si>
+  <si>
+    <t>[ IfcDoor ]</t>
+  </si>
+  <si>
+    <t>Incêndio</t>
+  </si>
+  <si>
+    <t>Vedação corta-fogo</t>
+  </si>
+  <si>
+    <t>Porta corta-fogo</t>
+  </si>
+  <si>
+    <t>Vedação.CF</t>
+  </si>
+  <si>
+    <t>Porta.CF</t>
+  </si>
+  <si>
+    <t>Shaft.CF</t>
+  </si>
+  <si>
+    <t>Selagem ao Fogo</t>
+  </si>
+  <si>
+    <t>Shaft corta-fogo</t>
+  </si>
+  <si>
+    <t>Paredes e divisórias que limitam a propagação das chamas graças às suas propriedades de resistência ao fogo, projetadas especificamente para essa função.</t>
+  </si>
+  <si>
+    <t>Shafts e passagens verticais projetados com selagem intumescente, dumpers antifumaça e barreiras corta-fogo em cada pavimento.</t>
+  </si>
+  <si>
+    <t>Sistemas.Passivos</t>
+  </si>
+  <si>
+    <t>De.Selagem</t>
+  </si>
+  <si>
+    <t>Sistemas.Ativos</t>
+  </si>
+  <si>
+    <t>De.Combate</t>
+  </si>
+  <si>
+    <t>Sprinkler.Pendente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprinkler.Upright </t>
+  </si>
+  <si>
+    <t>Sprinkler.Lateral</t>
+  </si>
+  <si>
+    <t>Sprinkler Pendente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprinkler Upright </t>
+  </si>
+  <si>
+    <t>Sprinkler Lateral</t>
+  </si>
+  <si>
+    <t>De Combate ao Fogo</t>
+  </si>
+  <si>
+    <t>Sprinkler Pendente é um chuveiro automático instalado no teto com o jato de água para baixo.</t>
+  </si>
+  <si>
+    <t>Sprinkler Upright é um chuveiro automático instalado em tubulação exposta abaixo do teto com o jato de água para cima.</t>
+  </si>
+  <si>
+    <t>Sprinkler Lateral é um chuveiro automático instalado em paredes, ideal para corredores.</t>
+  </si>
+  <si>
+    <t>[ OST_Walls ]</t>
+  </si>
+  <si>
+    <t>[ null ]</t>
+  </si>
+  <si>
+    <t>[ IfcPipeSegment : IfcPipeFitting ]</t>
+  </si>
+  <si>
+    <t>[ IfcFireSuppressionTerminalSPRINKLER : IfcPipeSegment : IfcPipeFitting]</t>
+  </si>
+  <si>
+    <t>[ OST_PipingSystem : OST_PipeSegments : OST_PipeFitting : OST_PipeCurves : OST_PipeConnections : OST_PipeFittingInsulation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Sprinklers : OST_PipingSystem : OST_PipeSegments : OST_PipeFitting : OST_PipeCurves : OST_PipeConnections : OST_PipeFittingInsulation ]]</t>
+  </si>
+  <si>
+    <t>SPK_ID_678250</t>
+  </si>
+  <si>
+    <t>SPK_ID_678251</t>
+  </si>
+  <si>
+    <t>SPK_ID_678252</t>
+  </si>
+  <si>
+    <t>SPK_ID_678253</t>
+  </si>
+  <si>
+    <t>SPK_ID_678256</t>
+  </si>
+  <si>
+    <t>SPK_ID_678254</t>
+  </si>
+  <si>
+    <t>SPK_ID_678255</t>
+  </si>
+  <si>
+    <t>SPK_ID_678257</t>
+  </si>
+  <si>
+    <t>SPK_ID_678258</t>
+  </si>
+  <si>
+    <t>SPK_ID_678259</t>
+  </si>
+  <si>
+    <t>SPK_ID_678260</t>
+  </si>
+  <si>
+    <t>SPK_ID_678261</t>
+  </si>
+  <si>
+    <t>Sis_Ativo_01</t>
+  </si>
+  <si>
+    <t>Sis_Ativo_02</t>
+  </si>
+  <si>
+    <t>"[ IfcFireSuppressionTerminalSPRINKLER : IfcPipeSegment : IfcPipeFitting ]"</t>
+  </si>
+  <si>
+    <t>"[ OST_Sprinklers : OST_PipeSegments : OST_PipeFitting ]"</t>
+  </si>
+  <si>
+    <t>"[ 3E.62.04 ]"</t>
+  </si>
+  <si>
+    <t>DET_ID_678342</t>
+  </si>
+  <si>
+    <t>DET_ID_678221</t>
+  </si>
+  <si>
+    <t>De Deteção de Fumaça</t>
+  </si>
+  <si>
+    <t>De.Detecção</t>
+  </si>
+  <si>
+    <t>Detector.Iônico</t>
+  </si>
+  <si>
+    <t>Detector.Óptico</t>
+  </si>
+  <si>
+    <t>Detector.Aspiração</t>
+  </si>
+  <si>
+    <t>Detector.Lineal</t>
+  </si>
+  <si>
+    <t>Detector.Combinado</t>
+  </si>
+  <si>
+    <t>Detector de fumaça iônico</t>
+  </si>
+  <si>
+    <t>Detector de fumaça óptico</t>
+  </si>
+  <si>
+    <t>Detector de fumaça por aspiração</t>
+  </si>
+  <si>
+    <t>Detector de fumaça lineal</t>
+  </si>
+  <si>
+    <t>Detector de fumaça combinado</t>
+  </si>
+  <si>
+    <t>Detector que integra detecção de fumaça e calor no mesmo dispositivo. Aumenta a confiabilidade, sendo indicado para ambientes industriais ou com variações de temperatura.</t>
+  </si>
+  <si>
+    <t>Detecta graças a um feixe de luz (laser ou infravermelho) entre emissor e receptor.</t>
+  </si>
+  <si>
+    <t>Detecta usando uma rede de tubos que aspira continuamente o ar do ambiente. Detecta partículas muito pequenas, permitindo detecção precoce. Ideal para data centers, museus, bibliotecas e ambientes críticos.</t>
+  </si>
+  <si>
+    <t>Detecta fumaça por meio da dispersão da luz em uma câmara interna. Mais eficaz em incêndios de combustão lenta (fumaça densa). É o tipo mais comum em edifícios residenciais e comerciais.</t>
+  </si>
+  <si>
+    <t>Detecta partículas muito pequenas de fumaça em incêndios de combustão rápida.</t>
+  </si>
+  <si>
+    <t>"Sistema Ativo para detecção de fumaça"</t>
+  </si>
+  <si>
+    <t>"[ 3E.62.20 ]"</t>
+  </si>
+  <si>
+    <t>"[ IfcSensorSMOKESENSOR ]"</t>
+  </si>
+  <si>
+    <t>"[ OST_FireProtection ]"</t>
+  </si>
+  <si>
+    <t>"Instância de Detector de fumaça do sistema INC02 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
+  </si>
+  <si>
+    <t>"Instância de Sprinkler do sistema INC02 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
+  </si>
+  <si>
+    <t>"Instância de Sprinkler do sistema INC01 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
+  </si>
+  <si>
+    <t>"Betta Sistemas Eletrônicos"</t>
+  </si>
+  <si>
+    <t>"Sistema Ativo de Extinção de Incêndio"</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1119,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1141,6 +1258,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1254,7 +1377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1440,57 +1563,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="29">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1588,6 +1671,24 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2213,7 +2314,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>93</v>
@@ -2369,7 +2470,7 @@
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C17" s="40" t="s">
         <v>93</v>
@@ -2381,7 +2482,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46216.38966828704</v>
+        <v>46224.648054398145</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>93</v>
@@ -2425,7 +2526,7 @@
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>93</v>
@@ -2436,7 +2537,7 @@
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C23" s="40" t="s">
         <v>94</v>
@@ -2462,32 +2563,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" style="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" style="54" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="54" customWidth="1"/>
+    <col min="5" max="5" width="10" style="54" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="62" customWidth="1"/>
+    <col min="7" max="11" width="6.7109375" style="54" customWidth="1"/>
     <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="54" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="54" customWidth="1"/>
+    <col min="16" max="16" width="83.85546875" style="54" customWidth="1"/>
+    <col min="17" max="17" width="88.7109375" style="54" customWidth="1"/>
     <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="54" customWidth="1"/>
+    <col min="22" max="22" width="4.7109375" style="54" customWidth="1"/>
     <col min="23" max="23" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.140625" style="55" customWidth="1"/>
+    <col min="24" max="24" width="65.85546875" style="54" customWidth="1"/>
+    <col min="25" max="25" width="35.5703125" style="55" customWidth="1"/>
     <col min="26" max="26" width="5.5703125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="82.140625" style="54" customWidth="1"/>
     <col min="28" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
@@ -2579,16 +2680,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="F2" s="57" t="s">
         <v>83</v>
@@ -2625,7 +2726,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>85</v>
@@ -2646,10 +2747,10 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W2" s="59" t="str">
-        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-INC-",A2)</f>
+        <f t="shared" ref="W2:W32" si="3">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
       <c r="X2" s="30" t="s">
@@ -2659,10 +2760,10 @@
         <v>9</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="AA2:AA40" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
@@ -2671,19 +2772,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2717,7 +2818,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>85</v>
@@ -2738,7 +2839,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2763,19 +2864,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -2809,7 +2910,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>85</v>
@@ -2830,7 +2931,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2855,19 +2956,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -2901,7 +3002,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>85</v>
@@ -2922,7 +3023,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2947,19 +3048,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -2993,7 +3094,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>85</v>
@@ -3014,7 +3115,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="3"/>
@@ -3039,19 +3140,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -3077,26 +3178,26 @@
         <v>Sis.Incêndio</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="R7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="30" t="str">
-        <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, ".", " ")</f>
+        <f t="shared" ref="S7:U23" si="7">SUBSTITUTE(C7, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
       <c r="T7" s="30" t="str">
-        <f t="shared" ref="T7:U20" si="8">SUBSTITUTE(D7, ".", " ")</f>
+        <f t="shared" ref="T7:U21" si="8">SUBSTITUTE(D7, ".", " ")</f>
         <v>Sis Incêndio</v>
       </c>
       <c r="U7" s="30" t="str">
@@ -3104,23 +3205,24 @@
         <v>Sistema Combate</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W7" s="59" t="str">
-        <f t="shared" ref="W7:W28" si="9">CONCATENATE("Key-INC-",A7)</f>
+        <f t="shared" si="3"/>
         <v>Key-INC-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA7" s="30" t="s">
-        <v>260</v>
+        <v>214</v>
+      </c>
+      <c r="AA7" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Building Fire Fighting System</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3128,20 +3230,20 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>132</v>
-      </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
       </c>
@@ -3158,25 +3260,25 @@
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" ref="L8:M23" si="10">CONCATENATE("", C8)</f>
+        <f t="shared" ref="L8:M24" si="9">CONCATENATE("", C8)</f>
         <v>Sistema.Predial</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="O8" s="33" t="str">
-        <f t="shared" ref="O8:O21" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O8:O22" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
         <v>Alarme</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
@@ -3194,23 +3296,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W8" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-8</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>199</v>
+        <v>214</v>
+      </c>
+      <c r="AA8" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Device that signals the existence of a condition or situation of danger.</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3218,19 +3321,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G9" s="61" t="s">
         <v>9</v>
@@ -3248,25 +3351,25 @@
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M9" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O9" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M9" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O9" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Campainha</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>9</v>
@@ -3284,23 +3387,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W9" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>200</v>
+        <v>214</v>
+      </c>
+      <c r="AA9" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Audible alarm.</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3308,19 +3412,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3338,25 +3442,25 @@
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M10" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O10" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M10" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N10" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O10" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
@@ -3374,23 +3478,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W10" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>183</v>
+        <v>214</v>
+      </c>
+      <c r="AA10" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3398,19 +3503,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3428,25 +3533,25 @@
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M11" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O11" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M11" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N11" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O11" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Lumínico</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="R11" s="30" t="s">
         <v>9</v>
@@ -3464,23 +3569,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W11" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>184</v>
+        <v>214</v>
+      </c>
+      <c r="AA11" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Visual light alarm.</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3488,19 +3594,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3518,25 +3624,25 @@
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M12" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O12" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M12" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N12" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O12" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Caixa Manual</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="R12" s="30" t="s">
         <v>9</v>
@@ -3554,23 +3660,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W12" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA12" s="30" t="s">
-        <v>201</v>
+        <v>214</v>
+      </c>
+      <c r="AA12" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,19 +3685,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3608,25 +3715,25 @@
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M13" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O13" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M13" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N13" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O13" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Detonador</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R13" s="30" t="s">
         <v>9</v>
@@ -3644,23 +3751,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W13" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>202</v>
+        <v>214</v>
+      </c>
+      <c r="AA13" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3668,19 +3776,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -3698,25 +3806,25 @@
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M14" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O14" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M14" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O14" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Sirene</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="R14" s="30" t="s">
         <v>9</v>
@@ -3734,23 +3842,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W14" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA14" s="30" t="s">
-        <v>203</v>
+        <v>214</v>
+      </c>
+      <c r="AA14" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Audible alarm produced by a siren.</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3758,19 +3867,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F15" s="57" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G15" s="61" t="s">
         <v>9</v>
@@ -3788,25 +3897,25 @@
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M15" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O15" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M15" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N15" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="O15" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Alarme Apito</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="R15" s="30" t="s">
         <v>9</v>
@@ -3824,23 +3933,24 @@
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W15" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA15" s="30" t="s">
-        <v>204</v>
+        <v>214</v>
+      </c>
+      <c r="AA15" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Audible alarm produced by a whistle.</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3848,19 +3958,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -3878,25 +3988,25 @@
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O16" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M16" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N16" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O16" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Terminal Combate Fogo</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
@@ -3914,23 +4024,24 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W16" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>205</v>
+        <v>214</v>
+      </c>
+      <c r="AA16" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3938,19 +4049,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -3968,25 +4079,25 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O17" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M17" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O17" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Mangueira Entrada</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="R17" s="30" t="s">
         <v>9</v>
@@ -4004,23 +4115,24 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W17" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>206</v>
+        <v>214</v>
+      </c>
+      <c r="AA17" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4028,19 +4140,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -4058,25 +4170,25 @@
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M18" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O18" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M18" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O18" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Mangueira Carretel</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="R18" s="30" t="s">
         <v>9</v>
@@ -4094,23 +4206,24 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W18" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA18" s="30" t="s">
-        <v>207</v>
+        <v>214</v>
+      </c>
+      <c r="AA18" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Support structure on which a hose can be wound.</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4118,19 +4231,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4148,25 +4261,25 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M19" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N19" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O19" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M19" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N19" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O19" s="33" t="str">
-        <f t="shared" si="11"/>
         <v>Mangueira Canhão</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="R19" s="30" t="s">
         <v>9</v>
@@ -4184,23 +4297,24 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W19" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA19" s="30" t="s">
-        <v>208</v>
+        <v>214</v>
+      </c>
+      <c r="AA19" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Fire monitor.</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4208,19 +4322,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4238,59 +4352,60 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="L20" si="11">CONCATENATE("", C20)</f>
         <v>Sistema.Predial</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="M20" si="12">CONCATENATE("", D20)</f>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="O20" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Hidrante</v>
+        <f t="shared" ref="O20" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F20),"."," ")," De "," de "))</f>
+        <v>Detetor de Fumaça</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="R20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S20" si="14">SUBSTITUTE(C20, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="T20" si="15">SUBSTITUTE(D20, ".", " ")</f>
         <v>Sis Incêndio</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="U20" si="16">SUBSTITUTE(E20, ".", " ")</f>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W20" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-20</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA20" s="30" t="s">
-        <v>209</v>
+        <v>214</v>
+      </c>
+      <c r="AA20" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Smoke detector.</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,19 +4413,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F21" s="57" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4328,25 +4443,25 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M21" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N21" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O21" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M21" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N21" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O21" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Sprinkler</v>
+        <v>Hidrante</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="R21" s="30" t="s">
         <v>9</v>
@@ -4356,31 +4471,32 @@
         <v>Sistema Predial</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sis Incêndio</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W21" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-21</v>
       </c>
       <c r="X21" s="30" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA21" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+      <c r="AA21" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4388,19 +4504,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F22" s="57" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4418,24 +4534,25 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M22" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N22" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O22" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M22" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N22" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O22" s="29" t="s">
-        <v>250</v>
+        <v>Sprinkler</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="R22" s="30" t="s">
         <v>9</v>
@@ -4453,43 +4570,44 @@
         <v>Peças de Incêndio</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W22" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-22</v>
       </c>
       <c r="X22" s="30" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA22" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="AA22" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>A device for spraying water from a pipe under pressure over an area.</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>176</v>
+        <v>218</v>
+      </c>
+      <c r="F23" s="57" t="s">
+        <v>168</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4507,59 +4625,59 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Predial</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="O23" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="P23" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q23" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T23" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U23" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças de Incêndio</v>
+      </c>
+      <c r="V23" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="P23" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q23" s="30" t="str">
-        <f t="shared" ref="Q23" si="12">_xlfn.TRANSLATE(P23,"pt","es")</f>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
-      </c>
-      <c r="R23" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="30" t="str">
-        <f t="shared" ref="S23:U28" si="13">SUBSTITUTE(C23, ".", " ")</f>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T23" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U23" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Peças de Incêndio</v>
-      </c>
-      <c r="V23" s="30" t="s">
-        <v>113</v>
-      </c>
       <c r="W23" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-23</v>
       </c>
       <c r="X23" s="30" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA23" s="30" t="s">
-        <v>217</v>
+        <v>214</v>
+      </c>
+      <c r="AA23" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4567,19 +4685,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>263</v>
+        <v>122</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4597,59 +4715,60 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" ref="L24:L27" si="14">CONCATENATE("", C24)</f>
+        <f t="shared" si="9"/>
         <v>Sistema.Predial</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" ref="M24:M27" si="15">CONCATENATE("", D24)</f>
+        <f t="shared" si="9"/>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q24" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P24,"pt","es")</f>
-        <v>Cisterna Superior</v>
+        <f t="shared" ref="Q24" si="17">_xlfn.TRANSLATE(P24,"pt","es")</f>
+        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
       </c>
       <c r="R24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S24" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="S24:U29" si="18">SUBSTITUTE(C24, ".", " ")</f>
         <v>Sistema Predial</v>
       </c>
       <c r="T24" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Sis Incêndio</v>
       </c>
       <c r="U24" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="18"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W24" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-24</v>
       </c>
-      <c r="X24" s="29" t="s">
-        <v>105</v>
+      <c r="X24" s="30" t="s">
+        <v>174</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA24" s="30" t="s">
         <v>214</v>
+      </c>
+      <c r="AA24" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4657,19 +4776,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>264</v>
+        <v>123</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -4687,59 +4806,60 @@
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="L25:L28" si="19">CONCATENATE("", C25)</f>
         <v>Sistema.Predial</v>
       </c>
       <c r="M25" s="33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="M25:M28" si="20">CONCATENATE("", D25)</f>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="O25" s="52" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="30" t="str">
-        <f t="shared" ref="Q25:Q27" si="16">_xlfn.TRANSLATE(P25,"pt","es")</f>
-        <v>Cisterna intermedia</v>
+        <f>_xlfn.TRANSLATE(P25,"pt","es")</f>
+        <v>Cisterna Superior</v>
       </c>
       <c r="R25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Sistema Predial</v>
       </c>
       <c r="T25" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Sis Incêndio</v>
       </c>
       <c r="U25" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W25" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA25" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
+      </c>
+      <c r="AA25" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Upper Cistern</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4747,19 +4867,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4777,59 +4897,60 @@
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>Sistema.Predial</v>
       </c>
       <c r="M26" s="33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>Sis.Incêndio</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="P26" s="52" t="s">
         <v>110</v>
       </c>
       <c r="Q26" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Cisterna Inferior</v>
+        <f t="shared" ref="Q26:Q32" si="21">_xlfn.TRANSLATE(P26,"pt","es")</f>
+        <v>Cisterna intermedia</v>
       </c>
       <c r="R26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Sistema Predial</v>
       </c>
       <c r="T26" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Sis Incêndio</v>
       </c>
       <c r="U26" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="W26" s="59" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>Key-INC-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA26" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
+      </c>
+      <c r="AA26" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Intermediate Cistern</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4837,89 +4958,90 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C27" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N27" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="P27" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="33" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M27" s="33" t="str">
-        <f t="shared" si="15"/>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N27" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="O27" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="P27" s="52" t="s">
+      <c r="Q27" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Cisterna Inferior</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T27" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U27" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V27" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W27" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-27</v>
+      </c>
+      <c r="X27" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y27" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="Q27" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Tubería de agua fría</v>
-      </c>
-      <c r="R27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T27" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U27" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V27" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="W27" s="59" t="str">
-        <f t="shared" si="9"/>
-        <v>Key-INC-27</v>
-      </c>
-      <c r="X27" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y27" s="29" t="s">
-        <v>104</v>
-      </c>
       <c r="Z27" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA27" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
+      </c>
+      <c r="AA27" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Lower Cistern</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4927,153 +5049,1249 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E28" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q28" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubería de agua fría</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T28" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U28" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V28" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W28" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-28</v>
+      </c>
+      <c r="X28" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y28" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z28" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA28" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Cold Water Pipe</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="60">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="33" t="str">
+        <f t="shared" ref="L29:L31" si="22">CONCATENATE("", C29)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M29" s="33" t="str">
+        <f t="shared" ref="M29:M31" si="23">CONCATENATE("", D29)</f>
+        <v>Sis.Incêndio</v>
+      </c>
+      <c r="N29" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="P29" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q29" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubería de agua fría</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="30" t="str">
+        <f t="shared" ref="S29:S31" si="24">SUBSTITUTE(C29, ".", " ")</f>
+        <v>Sistema Predial</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Sis Incêndio</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Tubulação de Incêndio</v>
+      </c>
+      <c r="V29" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W29" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-29</v>
+      </c>
+      <c r="X29" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y29" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z29" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA29" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Cold Water Pipe</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="60">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M30" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N30" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="O30" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="P30" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q30" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>La puerta cortafuegos que se cierra impide el paso del fuego y el humo.</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" ref="T30:T32" si="25">SUBSTITUTE(D30, ".", " ")</f>
+        <v>Sistemas Passivos</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" ref="U30:U32" si="26">SUBSTITUTE(E30, ".", " ")</f>
+        <v>De Selagem</v>
+      </c>
+      <c r="V30" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W30" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-30</v>
+      </c>
+      <c r="X30" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y30" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z30" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA30" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Fire door that closed prevents the passage of fire and smoke.</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="60">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M31" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N31" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="O31" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="P31" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q31" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Muros y tabiques que limitan la propagación de las llamas gracias a sus propiedades de resistencia al fuego, diseñados específicamente para esta función.</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T31" s="30" t="str">
+        <f t="shared" si="25"/>
+        <v>Sistemas Passivos</v>
+      </c>
+      <c r="U31" s="30" t="str">
+        <f t="shared" si="26"/>
+        <v>De Selagem</v>
+      </c>
+      <c r="V31" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W31" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-31</v>
+      </c>
+      <c r="X31" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA31" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="60">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="33" t="str">
+        <f t="shared" ref="L32:L34" si="27">CONCATENATE("", C32)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M32" s="33" t="str">
+        <f t="shared" ref="M32:M34" si="28">CONCATENATE("", D32)</f>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N32" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="O32" s="52" t="s">
+        <v>251</v>
+      </c>
+      <c r="P32" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q32" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Pozos y pasadizos verticales diseñados con sellado intumescente, volcadores sin humo y barreras cortafuego en cada planta.</v>
+      </c>
+      <c r="R32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S32" s="30" t="str">
+        <f t="shared" ref="S32:S34" si="29">SUBSTITUTE(C32, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T32" s="30" t="str">
+        <f t="shared" si="25"/>
+        <v>Sistemas Passivos</v>
+      </c>
+      <c r="U32" s="30" t="str">
+        <f t="shared" si="26"/>
+        <v>De Selagem</v>
+      </c>
+      <c r="V32" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W32" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-INC-32</v>
+      </c>
+      <c r="X32" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y32" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA32" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="60">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E33" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="33" t="str">
+        <f t="shared" ref="L33" si="30">CONCATENATE("", C33)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M33" s="33" t="str">
+        <f t="shared" ref="M33" si="31">CONCATENATE("", D33)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N33" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="O33" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="P33" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q33" s="30" t="str">
+        <f t="shared" ref="Q33:Q35" si="32">_xlfn.TRANSLATE(P33,"pt","es")</f>
+        <v>El colgante de aspersores es una ducha automática instalada en el techo con el chorro de agua hacia abajo.</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="30" t="str">
+        <f t="shared" ref="S33" si="33">SUBSTITUTE(C33, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T33" s="30" t="str">
+        <f t="shared" ref="T33:T35" si="34">SUBSTITUTE(D33, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U33" s="30" t="str">
+        <f t="shared" ref="U33:U35" si="35">SUBSTITUTE(E33, ".", " ")</f>
+        <v>De Combate</v>
+      </c>
+      <c r="V33" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W33" s="59" t="str">
+        <f t="shared" ref="W33:W35" si="36">CONCATENATE("Key-INC-",A33)</f>
+        <v>Key-INC-33</v>
+      </c>
+      <c r="X33" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y33" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z33" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA33" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="60">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L34" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M34" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N34" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="O34" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="P34" s="63" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q34" s="30" t="str">
+        <f t="shared" ref="Q34" si="37">_xlfn.TRANSLATE(P34,"pt","es")</f>
+        <v>El rociador vertical es una ducha automática instalada en tuberías expuestas bajo el techo con el chorro de agua hacia arriba.</v>
+      </c>
+      <c r="R34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S34" s="30" t="str">
+        <f t="shared" si="29"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T34" s="30" t="str">
+        <f t="shared" ref="T34" si="38">SUBSTITUTE(D34, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U34" s="30" t="str">
+        <f t="shared" ref="U34" si="39">SUBSTITUTE(E34, ".", " ")</f>
+        <v>De Combate</v>
+      </c>
+      <c r="V34" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W34" s="59" t="str">
+        <f t="shared" ref="W34" si="40">CONCATENATE("Key-INC-",A34)</f>
+        <v>Key-INC-34</v>
+      </c>
+      <c r="X34" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y34" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z34" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA34" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="60">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="33" t="str">
+        <f t="shared" ref="L35" si="41">CONCATENATE("", C35)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M35" s="33" t="str">
+        <f t="shared" ref="M35" si="42">CONCATENATE("", D35)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N35" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="O35" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="F28" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="G28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="33" t="str">
-        <f t="shared" ref="L28" si="17">CONCATENATE("", C28)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M28" s="33" t="str">
-        <f t="shared" ref="M28" si="18">CONCATENATE("", D28)</f>
-        <v>Sis.Incêndio</v>
-      </c>
-      <c r="N28" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="O28" s="52" t="s">
-        <v>249</v>
-      </c>
-      <c r="P28" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q28" s="30" t="str">
-        <f t="shared" ref="Q28" si="19">_xlfn.TRANSLATE(P28,"pt","es")</f>
-        <v>Tubería de agua fría</v>
-      </c>
-      <c r="R28" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="30" t="str">
-        <f t="shared" ref="S28" si="20">SUBSTITUTE(C28, ".", " ")</f>
-        <v>Sistema Predial</v>
-      </c>
-      <c r="T28" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Sis Incêndio</v>
-      </c>
-      <c r="U28" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V28" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="W28" s="59" t="str">
-        <f t="shared" si="9"/>
-        <v>Key-INC-28</v>
-      </c>
-      <c r="X28" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y28" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z28" s="30" t="s">
+      <c r="P35" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q35" s="30" t="str">
+        <f t="shared" si="32"/>
+        <v>El rociador lateral es una ducha automática instalada en las paredes, ideal para pasillos.</v>
+      </c>
+      <c r="R35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S35" s="30" t="str">
+        <f t="shared" ref="S35" si="43">SUBSTITUTE(C35, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T35" s="30" t="str">
+        <f t="shared" si="34"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U35" s="30" t="str">
+        <f t="shared" si="35"/>
+        <v>De Combate</v>
+      </c>
+      <c r="V35" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W35" s="59" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-INC-35</v>
+      </c>
+      <c r="X35" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y35" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z35" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA35" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="60">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AA28" s="30" t="s">
-        <v>213</v>
+      <c r="E36" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="33" t="str">
+        <f t="shared" ref="L36" si="44">CONCATENATE("", C36)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M36" s="33" t="str">
+        <f t="shared" ref="M36" si="45">CONCATENATE("", D36)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N36" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="O36" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="P36" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q36" s="30" t="str">
+        <f t="shared" ref="Q36" si="46">_xlfn.TRANSLATE(P36,"pt","es")</f>
+        <v>Detecta partículas muy pequeñas de humo en incendios de combustión rápida.</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S36" s="30" t="str">
+        <f t="shared" ref="S36" si="47">SUBSTITUTE(C36, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T36" s="30" t="str">
+        <f t="shared" ref="T36" si="48">SUBSTITUTE(D36, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U36" s="30" t="str">
+        <f t="shared" ref="U36" si="49">SUBSTITUTE(E36, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V36" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W36" s="59" t="str">
+        <f t="shared" ref="W36" si="50">CONCATENATE("Key-INC-",A36)</f>
+        <v>Key-INC-36</v>
+      </c>
+      <c r="X36" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y36" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z36" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA36" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Detects very small particles of smoke in fast-burning fires.</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="60">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="33" t="str">
+        <f t="shared" ref="L37:L38" si="51">CONCATENATE("", C37)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M37" s="33" t="str">
+        <f t="shared" ref="M37:M38" si="52">CONCATENATE("", D37)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N37" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="O37" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="P37" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q37" s="30" t="str">
+        <f t="shared" ref="Q37:Q38" si="53">_xlfn.TRANSLATE(P37,"pt","es")</f>
+        <v>Detecta el humo dispersando la luz en una cámara interna. Más efectivo en incendios latentes (humo denso). Es el tipo más común en edificios residenciales y comerciales.</v>
+      </c>
+      <c r="R37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S37" s="30" t="str">
+        <f t="shared" ref="S37:S38" si="54">SUBSTITUTE(C37, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T37" s="30" t="str">
+        <f t="shared" ref="T37:T38" si="55">SUBSTITUTE(D37, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U37" s="30" t="str">
+        <f t="shared" ref="U37:U38" si="56">SUBSTITUTE(E37, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V37" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W37" s="59" t="str">
+        <f t="shared" ref="W37:W38" si="57">CONCATENATE("Key-INC-",A37)</f>
+        <v>Key-INC-37</v>
+      </c>
+      <c r="X37" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y37" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z37" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA37" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="60">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M38" s="33" t="str">
+        <f t="shared" si="52"/>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N38" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="O38" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="P38" s="63" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q38" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Detecta el uso de una red de tuberías que succiona continuamente aire del entorno. Detecta partículas muy pequeñas, permitiendo una detección temprana. Ideal para centros de datos, museos, bibliotecas y entornos críticos.</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" s="30" t="str">
+        <f t="shared" si="54"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T38" s="30" t="str">
+        <f t="shared" si="55"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U38" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De Detecção</v>
+      </c>
+      <c r="V38" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W38" s="59" t="str">
+        <f t="shared" si="57"/>
+        <v>Key-INC-38</v>
+      </c>
+      <c r="X38" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y38" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z38" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA38" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="60">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="33" t="str">
+        <f t="shared" ref="L39" si="58">CONCATENATE("", C39)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M39" s="33" t="str">
+        <f t="shared" ref="M39" si="59">CONCATENATE("", D39)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N39" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="O39" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="P39" s="63" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q39" s="30" t="str">
+        <f t="shared" ref="Q39" si="60">_xlfn.TRANSLATE(P39,"pt","es")</f>
+        <v>Detecta gracias a un haz de luz (láser o infrarrojo) entre el emisor y el receptor.</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S39" s="30" t="str">
+        <f t="shared" ref="S39" si="61">SUBSTITUTE(C39, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T39" s="30" t="str">
+        <f t="shared" ref="T39" si="62">SUBSTITUTE(D39, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U39" s="30" t="str">
+        <f t="shared" ref="U39" si="63">SUBSTITUTE(E39, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V39" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W39" s="59" t="str">
+        <f t="shared" ref="W39" si="64">CONCATENATE("Key-INC-",A39)</f>
+        <v>Key-INC-39</v>
+      </c>
+      <c r="X39" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y39" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z39" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA39" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="60">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="33" t="str">
+        <f t="shared" ref="L40" si="65">CONCATENATE("", C40)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M40" s="33" t="str">
+        <f t="shared" ref="M40" si="66">CONCATENATE("", D40)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N40" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="O40" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="P40" s="63" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q40" s="30" t="str">
+        <f t="shared" ref="Q40" si="67">_xlfn.TRANSLATE(P40,"pt","es")</f>
+        <v>Detector que integra detección de humo y calor en el mismo dispositivo. Aumenta la fiabilidad, estando indicado para entornos industriales o con variaciones de temperatura.</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S40" s="30" t="str">
+        <f t="shared" ref="S40" si="68">SUBSTITUTE(C40, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T40" s="30" t="str">
+        <f t="shared" ref="T40" si="69">SUBSTITUTE(D40, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U40" s="30" t="str">
+        <f t="shared" ref="U40" si="70">SUBSTITUTE(E40, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V40" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="W40" s="59" t="str">
+        <f t="shared" ref="W40" si="71">CONCATENATE("Key-INC-",A40)</f>
+        <v>Key-INC-40</v>
+      </c>
+      <c r="X40" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y40" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z40" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA40" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Detector that integrates smoke and heat detection in the same device. Increases reliability, being indicated for industrial environments or with temperature variations.</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA895">
-    <sortCondition ref="F7:F895"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA888">
+    <sortCondition ref="F7:F888"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="30" priority="1508"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F22">
-    <cfRule type="duplicateValues" dxfId="25" priority="1552"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="24" priority="1530"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1480"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1501"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O17:O22 A1:D1 F1:O1 Q1:X1 Z1:AA1 S7:S28 E8:F16 L8:O16 Q8:Q22 X8:Y22 AA8:XFD22 F17:F22 L17:M22 E17:E23 N17:N23">
-    <cfRule type="cellIs" dxfId="19" priority="72" operator="equal">
+  <conditionalFormatting sqref="A2:B40">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O22">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  <conditionalFormatting sqref="F1 F7 F24:F1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="1536"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23:O28">
-    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="26" priority="1514"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7">
-    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="25" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X23">
-    <cfRule type="cellIs" dxfId="15" priority="24" operator="equal">
+  <conditionalFormatting sqref="F8:F23">
+    <cfRule type="duplicateValues" dxfId="21" priority="1558"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1507"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O21:O23 A1:D1 F1:O1 Q1:X1 Z1:AA1 E8:F20 L8:O20 Q8:Q23 X8:Y23 AB8:XFD23 F21:F23 L21:M23 E21:E24 N21:N24">
+    <cfRule type="cellIs" dxfId="16" priority="78" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
+  <conditionalFormatting sqref="O23">
+    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O24:O32">
+    <cfRule type="duplicateValues" dxfId="14" priority="1565"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33:O40">
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7">
+    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S40">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA23:AA28">
-    <cfRule type="cellIs" dxfId="13" priority="25" operator="equal">
+  <conditionalFormatting sqref="X24">
+    <cfRule type="cellIs" dxfId="10" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="X33:X40">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA40">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5290,7 +6508,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5303,1101 +6521,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
-  <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="R1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="S1" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
-        <v>2</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="J4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
-        <v>4</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L5" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N5" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P5" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="R5" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
-        <v>5</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L6" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N6" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P6" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="R6" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
-        <v>6</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L7" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N7" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P7" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R7" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S7" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
-        <v>7</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L8" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N8" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P8" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R8" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S8" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
-        <v>8</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H9" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L9" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N9" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P9" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q9" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R9" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L10" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N10" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P10" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S10" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
-        <v>10</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L11" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M11" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N11" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P11" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q11" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R11" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S11" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
-        <v>11</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L12" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N12" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P12" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S12" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
-        <v>12</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L13" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M13" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N13" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P13" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q13" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R13" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S13" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
-        <v>13</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L14" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P14" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R14" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S14" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
-        <v>14</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L15" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M15" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N15" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P15" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R15" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S15" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
-        <v>15</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D16" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L16" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M16" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N16" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P16" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R16" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S16" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
-        <v>16</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L17" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N17" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P17" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q17" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R17" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S17" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
-        <v>17</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="D18" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L18" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="M18" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N18" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="P18" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R18" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="S18" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
@@ -6461,25 +6584,1359 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
+  <sheetPr codeName="Planilha4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="56.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" customWidth="1"/>
+    <col min="17" max="17" width="31.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
+        <v>3</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>4</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
+        <v>5</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L5" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P5" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="R5" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>6</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L6" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P6" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="R6" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>7</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L7" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P7" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R7" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S7" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>8</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P8" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q8" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R8" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S8" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>9</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L9" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P9" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R9" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>10</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L10" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P10" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R10" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>11</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P11" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R11" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>12</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L12" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P12" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R12" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>13</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J13" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L13" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P13" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R13" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S13" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
+        <v>14</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L14" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P14" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R14" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S14" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>15</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L15" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O15" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P15" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R15" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S15" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
+        <v>16</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N16" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O16" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P16" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R16" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S16" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>17</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J17" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L17" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N17" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P17" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R17" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S17" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="20">
+        <v>18</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P18" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R18" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S18" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
+        <v>19</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L19" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N19" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O19" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P19" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R19" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S19" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
+        <v>20</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L20" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N20" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O20" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="P20" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q20" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R20" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S20" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
+        <v>21</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="L21" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="N21" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O21" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="P21" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q21" s="64" t="s">
+        <v>312</v>
+      </c>
+      <c r="R21" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S21" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20">
+        <v>22</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="L22" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="N22" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O22" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="P22" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q22" s="64" t="s">
+        <v>312</v>
+      </c>
+      <c r="R22" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A201C1EB-F585-4887-A7A4-57930AECCDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94FEEA4-231C-4912-BD2B-8884F937D289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="318">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -392,9 +392,6 @@
     <t>"Indivíduo Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
-    <t>Sistema.Predial</t>
-  </si>
-  <si>
     <t>Cisterna Superior</t>
   </si>
   <si>
@@ -440,9 +437,6 @@
     <t>Sistema.Combate</t>
   </si>
   <si>
-    <t>Sis.Incêndio</t>
-  </si>
-  <si>
     <t>Reserva.Superior</t>
   </si>
   <si>
@@ -773,9 +767,6 @@
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1029,6 +1020,12 @@
   </si>
   <si>
     <t>"Sistema Ativo de Extinção de Incêndio"</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Sistemas.Prediais</t>
   </si>
 </sst>
 </file>
@@ -2279,15 +2276,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2298,7 +2295,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2309,18 +2306,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2331,7 +2328,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2343,7 +2340,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2355,7 +2352,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2366,7 +2363,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2377,7 +2374,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2388,7 +2385,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2399,7 +2396,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2410,7 +2407,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2421,7 +2418,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2432,7 +2429,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2443,7 +2440,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2454,7 +2451,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2465,30 +2462,30 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46224.648054398145</v>
+        <v>46243.524946064812</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2499,7 +2496,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2510,7 +2507,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2521,29 +2518,29 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>91</v>
       </c>
@@ -2564,35 +2561,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="54" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" style="54" customWidth="1"/>
     <col min="5" max="5" width="10" style="54" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="62" customWidth="1"/>
-    <col min="7" max="11" width="6.7109375" style="54" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.15234375" style="62" customWidth="1"/>
+    <col min="7" max="11" width="6.69140625" style="54" customWidth="1"/>
+    <col min="12" max="12" width="8.84375" style="54" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" style="54" customWidth="1"/>
-    <col min="16" max="16" width="83.85546875" style="54" customWidth="1"/>
-    <col min="17" max="17" width="88.7109375" style="54" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="54" customWidth="1"/>
-    <col min="22" max="22" width="4.7109375" style="54" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="65.85546875" style="54" customWidth="1"/>
-    <col min="25" max="25" width="35.5703125" style="55" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="82.140625" style="54" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="54"/>
+    <col min="14" max="14" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.69140625" style="54" customWidth="1"/>
+    <col min="16" max="16" width="83.84375" style="54" customWidth="1"/>
+    <col min="17" max="17" width="88.69140625" style="54" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.3828125" style="54" customWidth="1"/>
+    <col min="22" max="22" width="4.69140625" style="54" customWidth="1"/>
+    <col min="23" max="23" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="65.84375" style="54" customWidth="1"/>
+    <col min="25" max="25" width="35.53515625" style="55" customWidth="1"/>
+    <col min="26" max="26" width="5.53515625" style="54" customWidth="1"/>
+    <col min="27" max="27" width="82.15234375" style="54" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>96</v>
       </c>
@@ -2675,21 +2672,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F2" s="57" t="s">
         <v>83</v>
@@ -2726,7 +2723,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>85</v>
@@ -2747,7 +2744,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W2" s="59" t="str">
         <f t="shared" ref="W2:W32" si="3">CONCATENATE("Key-INC-",A2)</f>
@@ -2760,31 +2757,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA40" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2818,7 +2815,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>85</v>
@@ -2839,7 +2836,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2859,24 +2856,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -2910,7 +2907,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>85</v>
@@ -2931,7 +2928,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2951,24 +2948,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -3002,7 +2999,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>85</v>
@@ -3023,7 +3020,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="3"/>
@@ -3043,24 +3040,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -3094,7 +3091,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>85</v>
@@ -3115,7 +3112,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="3"/>
@@ -3135,24 +3132,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -3171,78 +3168,78 @@
       </c>
       <c r="L7" s="33" t="str">
         <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
         <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="30" t="str">
         <f t="shared" ref="S7:U23" si="7">SUBSTITUTE(C7, ".", " ")</f>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T7" s="30" t="str">
         <f t="shared" ref="T7:U21" si="8">SUBSTITUTE(D7, ".", " ")</f>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U7" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema Combate</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA7" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Building Fire Fighting System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
@@ -3261,79 +3258,79 @@
       </c>
       <c r="L8" s="33" t="str">
         <f t="shared" ref="L8:M24" si="9">CONCATENATE("", C8)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O8" s="33" t="str">
         <f t="shared" ref="O8:O22" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
         <v>Alarme</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T8" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U8" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-8</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Device that signals the existence of a condition or situation of danger.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G9" s="61" t="s">
         <v>9</v>
@@ -3352,79 +3349,79 @@
       </c>
       <c r="L9" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M9" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O9" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Campainha</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T9" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U9" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA9" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Audible alarm.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3443,79 +3440,79 @@
       </c>
       <c r="L10" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O10" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T10" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U10" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W10" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA10" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3534,79 +3531,79 @@
       </c>
       <c r="L11" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O11" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Lumínico</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T11" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U11" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W11" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA11" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Visual light alarm.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3625,79 +3622,79 @@
       </c>
       <c r="L12" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O12" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Caixa Manual</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R12" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T12" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U12" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W12" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA12" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3716,79 +3713,79 @@
       </c>
       <c r="L13" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O13" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Detonador</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R13" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T13" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U13" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W13" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA13" s="30" t="str">
         <f t="shared" si="4"/>
         <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -3807,79 +3804,79 @@
       </c>
       <c r="L14" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O14" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Sirene</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R14" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T14" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U14" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W14" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA14" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Audible alarm produced by a siren.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F15" s="57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G15" s="61" t="s">
         <v>9</v>
@@ -3898,79 +3895,79 @@
       </c>
       <c r="L15" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O15" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Alarme Apito</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T15" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U15" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W15" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA15" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Audible alarm produced by a whistle.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -3989,79 +3986,79 @@
       </c>
       <c r="L16" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O16" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Terminal Combate Fogo</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T16" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U16" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W16" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA16" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -4080,79 +4077,79 @@
       </c>
       <c r="L17" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O17" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Mangueira Entrada</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T17" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U17" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W17" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA17" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -4171,79 +4168,79 @@
       </c>
       <c r="L18" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O18" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Mangueira Carretel</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T18" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U18" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W18" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA18" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Support structure on which a hose can be wound.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4262,79 +4259,79 @@
       </c>
       <c r="L19" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O19" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Mangueira Canhão</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="R19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T19" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U19" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W19" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA19" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Fire monitor.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" s="57" t="s">
         <v>233</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>236</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4353,79 +4350,79 @@
       </c>
       <c r="L20" s="33" t="str">
         <f t="shared" ref="L20" si="11">CONCATENATE("", C20)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
         <f t="shared" ref="M20" si="12">CONCATENATE("", D20)</f>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O20" s="33" t="str">
         <f t="shared" ref="O20" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F20),"."," ")," De "," de "))</f>
         <v>Detetor de Fumaça</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="30" t="str">
         <f t="shared" ref="S20" si="14">SUBSTITUTE(C20, ".", " ")</f>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T20" s="30" t="str">
         <f t="shared" ref="T20" si="15">SUBSTITUTE(D20, ".", " ")</f>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U20" s="30" t="str">
         <f t="shared" ref="U20" si="16">SUBSTITUTE(E20, ".", " ")</f>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W20" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-20</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA20" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Smoke detector.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F21" s="57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4444,79 +4441,79 @@
       </c>
       <c r="L21" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O21" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Hidrante</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T21" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U21" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W21" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-21</v>
       </c>
       <c r="X21" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA21" s="30" t="str">
         <f t="shared" si="4"/>
         <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F22" s="57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4535,79 +4532,79 @@
       </c>
       <c r="L22" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O22" s="33" t="str">
         <f t="shared" si="10"/>
         <v>Sprinkler</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T22" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U22" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W22" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-22</v>
       </c>
       <c r="X22" s="30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA22" s="30" t="str">
         <f t="shared" si="4"/>
         <v>A device for spraying water from a pipe under pressure over an area.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F23" s="57" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4626,78 +4623,78 @@
       </c>
       <c r="L23" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O23" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T23" s="30" t="str">
         <f t="shared" si="7"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U23" s="30" t="str">
         <f t="shared" si="7"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W23" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-23</v>
       </c>
       <c r="X23" s="30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA23" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4716,20 +4713,20 @@
       </c>
       <c r="L24" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q24" s="30" t="str">
         <f t="shared" ref="Q24" si="17">_xlfn.TRANSLATE(P24,"pt","es")</f>
@@ -4740,55 +4737,55 @@
       </c>
       <c r="S24" s="30" t="str">
         <f t="shared" ref="S24:U29" si="18">SUBSTITUTE(C24, ".", " ")</f>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T24" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U24" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W24" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-24</v>
       </c>
       <c r="X24" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y24" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="Y24" s="29" t="s">
-        <v>176</v>
-      </c>
       <c r="Z24" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA24" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -4807,20 +4804,20 @@
       </c>
       <c r="L25" s="33" t="str">
         <f t="shared" ref="L25:L28" si="19">CONCATENATE("", C25)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
         <f t="shared" ref="M25:M28" si="20">CONCATENATE("", D25)</f>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O25" s="52" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f>_xlfn.TRANSLATE(P25,"pt","es")</f>
@@ -4831,55 +4828,55 @@
       </c>
       <c r="S25" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T25" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U25" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W25" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA25" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Upper Cistern</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4898,20 +4895,20 @@
       </c>
       <c r="L26" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="33" t="str">
         <f t="shared" si="20"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P26" s="52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="30" t="str">
         <f t="shared" ref="Q26:Q32" si="21">_xlfn.TRANSLATE(P26,"pt","es")</f>
@@ -4922,55 +4919,55 @@
       </c>
       <c r="S26" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T26" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U26" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W26" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA26" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Intermediate Cistern</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="F27" s="42" t="s">
         <v>122</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>124</v>
       </c>
       <c r="G27" s="61" t="s">
         <v>9</v>
@@ -4989,20 +4986,20 @@
       </c>
       <c r="L27" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="33" t="str">
         <f t="shared" si="20"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O27" s="52" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5013,55 +5010,55 @@
       </c>
       <c r="S27" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T27" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U27" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W27" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z27" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA27" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Lower Cistern</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
@@ -5080,20 +5077,20 @@
       </c>
       <c r="L28" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="33" t="str">
         <f t="shared" si="20"/>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N28" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O28" s="52" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P28" s="52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q28" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5104,55 +5101,55 @@
       </c>
       <c r="S28" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T28" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U28" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W28" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA28" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
@@ -5171,20 +5168,20 @@
       </c>
       <c r="L29" s="33" t="str">
         <f t="shared" ref="L29:L31" si="22">CONCATENATE("", C29)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="33" t="str">
         <f t="shared" ref="M29:M31" si="23">CONCATENATE("", D29)</f>
-        <v>Sis.Incêndio</v>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N29" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O29" s="52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P29" s="52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5195,55 +5192,55 @@
       </c>
       <c r="S29" s="30" t="str">
         <f t="shared" ref="S29:S31" si="24">SUBSTITUTE(C29, ".", " ")</f>
-        <v>Sistema Predial</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T29" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Sis Incêndio</v>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U29" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Tubulação de Incêndio</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W29" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-29</v>
       </c>
       <c r="X29" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y29" s="29" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Z29" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA29" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G30" s="61" t="s">
         <v>9</v>
@@ -5269,13 +5266,13 @@
         <v>Sistemas.Passivos</v>
       </c>
       <c r="N30" s="33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O30" s="52" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P30" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q30" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5297,44 +5294,44 @@
         <v>De Selagem</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W30" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-30</v>
       </c>
       <c r="X30" s="29" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Y30" s="29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA30" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Fire door that closed prevents the passage of fire and smoke.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G31" s="61" t="s">
         <v>9</v>
@@ -5360,13 +5357,13 @@
         <v>Sistemas.Passivos</v>
       </c>
       <c r="N31" s="33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O31" s="52" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P31" s="52" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q31" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5388,44 +5385,44 @@
         <v>De Selagem</v>
       </c>
       <c r="V31" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W31" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-31</v>
       </c>
       <c r="X31" s="29" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Y31" s="29" t="s">
         <v>9</v>
       </c>
       <c r="Z31" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA31" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G32" s="61" t="s">
         <v>9</v>
@@ -5451,13 +5448,13 @@
         <v>Sistemas.Passivos</v>
       </c>
       <c r="N32" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="O32" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="P32" s="52" t="s">
         <v>250</v>
-      </c>
-      <c r="O32" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="P32" s="52" t="s">
-        <v>253</v>
       </c>
       <c r="Q32" s="30" t="str">
         <f t="shared" si="21"/>
@@ -5479,44 +5476,44 @@
         <v>De Selagem</v>
       </c>
       <c r="V32" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W32" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-INC-32</v>
       </c>
       <c r="X32" s="29" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Y32" s="29" t="s">
         <v>9</v>
       </c>
       <c r="Z32" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA32" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G33" s="61" t="s">
         <v>9</v>
@@ -5542,13 +5539,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N33" s="52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O33" s="52" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P33" s="63" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q33" s="30" t="str">
         <f t="shared" ref="Q33:Q35" si="32">_xlfn.TRANSLATE(P33,"pt","es")</f>
@@ -5570,44 +5567,44 @@
         <v>De Combate</v>
       </c>
       <c r="V33" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W33" s="59" t="str">
         <f t="shared" ref="W33:W35" si="36">CONCATENATE("Key-INC-",A33)</f>
         <v>Key-INC-33</v>
       </c>
       <c r="X33" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y33" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z33" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA33" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F34" s="42" t="s">
         <v>256</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>259</v>
       </c>
       <c r="G34" s="61" t="s">
         <v>9</v>
@@ -5633,13 +5630,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N34" s="52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O34" s="52" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P34" s="63" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q34" s="30" t="str">
         <f t="shared" ref="Q34" si="37">_xlfn.TRANSLATE(P34,"pt","es")</f>
@@ -5661,44 +5658,44 @@
         <v>De Combate</v>
       </c>
       <c r="V34" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W34" s="59" t="str">
         <f t="shared" ref="W34" si="40">CONCATENATE("Key-INC-",A34)</f>
         <v>Key-INC-34</v>
       </c>
       <c r="X34" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y34" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z34" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA34" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E35" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" s="42" t="s">
         <v>257</v>
-      </c>
-      <c r="F35" s="42" t="s">
-        <v>260</v>
       </c>
       <c r="G35" s="61" t="s">
         <v>9</v>
@@ -5724,13 +5721,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N35" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="O35" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="P35" s="63" t="s">
         <v>264</v>
-      </c>
-      <c r="O35" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="P35" s="63" t="s">
-        <v>267</v>
       </c>
       <c r="Q35" s="30" t="str">
         <f t="shared" si="32"/>
@@ -5752,44 +5749,44 @@
         <v>De Combate</v>
       </c>
       <c r="V35" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W35" s="59" t="str">
         <f t="shared" si="36"/>
         <v>Key-INC-35</v>
       </c>
       <c r="X35" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y35" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z35" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA35" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G36" s="61" t="s">
         <v>9</v>
@@ -5815,13 +5812,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N36" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O36" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P36" s="63" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q36" s="30" t="str">
         <f t="shared" ref="Q36" si="46">_xlfn.TRANSLATE(P36,"pt","es")</f>
@@ -5843,44 +5840,44 @@
         <v>De Detecção</v>
       </c>
       <c r="V36" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W36" s="59" t="str">
         <f t="shared" ref="W36" si="50">CONCATENATE("Key-INC-",A36)</f>
         <v>Key-INC-36</v>
       </c>
       <c r="X36" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y36" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z36" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA36" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Detects very small particles of smoke in fast-burning fires.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="60">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G37" s="61" t="s">
         <v>9</v>
@@ -5906,13 +5903,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N37" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O37" s="52" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P37" s="63" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q37" s="30" t="str">
         <f t="shared" ref="Q37:Q38" si="53">_xlfn.TRANSLATE(P37,"pt","es")</f>
@@ -5934,44 +5931,44 @@
         <v>De Detecção</v>
       </c>
       <c r="V37" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W37" s="59" t="str">
         <f t="shared" ref="W37:W38" si="57">CONCATENATE("Key-INC-",A37)</f>
         <v>Key-INC-37</v>
       </c>
       <c r="X37" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y37" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z37" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA37" s="30" t="str">
         <f t="shared" si="4"/>
         <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E38" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="42" t="s">
         <v>294</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>297</v>
       </c>
       <c r="G38" s="61" t="s">
         <v>9</v>
@@ -5997,13 +5994,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N38" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O38" s="52" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P38" s="63" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="Q38" s="30" t="str">
         <f t="shared" si="53"/>
@@ -6025,44 +6022,44 @@
         <v>De Detecção</v>
       </c>
       <c r="V38" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W38" s="59" t="str">
         <f t="shared" si="57"/>
         <v>Key-INC-38</v>
       </c>
       <c r="X38" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y38" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z38" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA38" s="30" t="str">
         <f t="shared" si="4"/>
         <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="60">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G39" s="61" t="s">
         <v>9</v>
@@ -6088,13 +6085,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N39" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O39" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="P39" s="63" t="s">
         <v>303</v>
-      </c>
-      <c r="P39" s="63" t="s">
-        <v>306</v>
       </c>
       <c r="Q39" s="30" t="str">
         <f t="shared" ref="Q39" si="60">_xlfn.TRANSLATE(P39,"pt","es")</f>
@@ -6116,44 +6113,44 @@
         <v>De Detecção</v>
       </c>
       <c r="V39" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W39" s="59" t="str">
         <f t="shared" ref="W39" si="64">CONCATENATE("Key-INC-",A39)</f>
         <v>Key-INC-39</v>
       </c>
       <c r="X39" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y39" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z39" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA39" s="30" t="str">
         <f t="shared" si="4"/>
         <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="60">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G40" s="61" t="s">
         <v>9</v>
@@ -6179,13 +6176,13 @@
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N40" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O40" s="52" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P40" s="63" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="Q40" s="30" t="str">
         <f t="shared" ref="Q40" si="67">_xlfn.TRANSLATE(P40,"pt","es")</f>
@@ -6207,20 +6204,20 @@
         <v>De Detecção</v>
       </c>
       <c r="V40" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W40" s="59" t="str">
         <f t="shared" ref="W40" si="71">CONCATENATE("Key-INC-",A40)</f>
         <v>Key-INC-40</v>
       </c>
       <c r="X40" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y40" s="29" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z40" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA40" s="30" t="str">
         <f t="shared" si="4"/>
@@ -6303,15 +6300,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6376,7 +6373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6441,7 +6438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6524,15 +6521,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6555,7 +6552,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6611,30 +6608,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="56.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="10.3828125" customWidth="1"/>
+    <col min="4" max="4" width="7.84375" customWidth="1"/>
+    <col min="5" max="5" width="7.53515625" customWidth="1"/>
+    <col min="6" max="6" width="5.15234375" customWidth="1"/>
+    <col min="7" max="7" width="56.15234375" customWidth="1"/>
+    <col min="8" max="8" width="5.15234375" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.42578125" customWidth="1"/>
-    <col min="17" max="17" width="31.85546875" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="6.84375" customWidth="1"/>
+    <col min="11" max="11" width="18.69140625" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.3828125" customWidth="1"/>
+    <col min="14" max="14" width="6.69140625" customWidth="1"/>
+    <col min="15" max="15" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.3828125" customWidth="1"/>
+    <col min="17" max="17" width="31.84375" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6693,7 +6690,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6752,15 +6749,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
@@ -6772,13 +6769,13 @@
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -6808,18 +6805,18 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>82</v>
@@ -6831,13 +6828,13 @@
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J4" s="49" t="s">
         <v>9</v>
@@ -6867,45 +6864,45 @@
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M5" s="24" t="s">
         <v>101</v>
@@ -6914,57 +6911,57 @@
         <v>100</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P5" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R5" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L6" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M6" s="24" t="s">
         <v>101</v>
@@ -6973,57 +6970,57 @@
         <v>100</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P6" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R6" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M7" s="24" t="s">
         <v>101</v>
@@ -7032,57 +7029,57 @@
         <v>100</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P7" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R7" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H8" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L8" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M8" s="24" t="s">
         <v>101</v>
@@ -7091,57 +7088,57 @@
         <v>100</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P8" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R8" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D9" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K9" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L9" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M9" s="24" t="s">
         <v>101</v>
@@ -7150,57 +7147,57 @@
         <v>100</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P9" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R9" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D10" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L10" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M10" s="24" t="s">
         <v>101</v>
@@ -7209,57 +7206,57 @@
         <v>100</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P10" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R10" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L11" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M11" s="24" t="s">
         <v>101</v>
@@ -7268,57 +7265,57 @@
         <v>100</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P11" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R11" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D12" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H12" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M12" s="24" t="s">
         <v>101</v>
@@ -7327,57 +7324,57 @@
         <v>100</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P12" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R12" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H13" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L13" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M13" s="24" t="s">
         <v>101</v>
@@ -7386,57 +7383,57 @@
         <v>100</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P13" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R13" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D14" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H14" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L14" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>101</v>
@@ -7445,57 +7442,57 @@
         <v>100</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P14" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R14" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L15" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M15" s="24" t="s">
         <v>101</v>
@@ -7504,57 +7501,57 @@
         <v>100</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P15" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R15" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D16" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>101</v>
@@ -7563,57 +7560,57 @@
         <v>100</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P16" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R16" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M17" s="24" t="s">
         <v>101</v>
@@ -7622,57 +7619,57 @@
         <v>100</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P17" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R17" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D18" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H18" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L18" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M18" s="24" t="s">
         <v>101</v>
@@ -7681,57 +7678,57 @@
         <v>100</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P18" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R18" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20">
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D19" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H19" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L19" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M19" s="24" t="s">
         <v>101</v>
@@ -7740,57 +7737,57 @@
         <v>100</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P19" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R19" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20">
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D20" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J20" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L20" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M20" s="24" t="s">
         <v>101</v>
@@ -7799,137 +7796,137 @@
         <v>100</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P20" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R20" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20">
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D21" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H21" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L21" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N21" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O21" s="24" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="P21" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q21" s="64" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="R21" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20">
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D22" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H22" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J22" s="49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L22" s="49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N22" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="P22" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q22" s="64" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="R22" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/INCE/Ontologia_Incendio.xlsx
+++ b/Versão5/INCE/Ontologia_Incendio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94FEEA4-231C-4912-BD2B-8884F937D289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53C8499-09BC-4323-88D1-623EF11E316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="299">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -321,15 +321,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>CategoriaRvt</t>
   </si>
   <si>
@@ -389,9 +380,6 @@
     <t>é.pertencente.a</t>
   </si>
   <si>
-    <t>"Indivíduo Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
-  </si>
-  <si>
     <t>Cisterna Superior</t>
   </si>
   <si>
@@ -647,9 +635,6 @@
     <t>Sis_INC_01</t>
   </si>
   <si>
-    <t>"Indivíduo Conteiner que representa um sistema de Combate a Incêndio do projeto"</t>
-  </si>
-  <si>
     <t>SPK_ID_453908</t>
   </si>
   <si>
@@ -668,12 +653,6 @@
     <t>"Sistema de Incêndio 2 do Predio"</t>
   </si>
   <si>
-    <t>"[ OST_Sprinklers ]"</t>
-  </si>
-  <si>
-    <t>"[ IfcFireSuppressionTerminalSPRINKLER ]"</t>
-  </si>
-  <si>
     <t>Acessório de Instalação de Incêndio</t>
   </si>
   <si>
@@ -731,48 +710,12 @@
     <t>Reserva.Intermediária</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>quem.fabricou</t>
   </si>
   <si>
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
-  </si>
-  <si>
     <t>Detetor.de.Fumaça</t>
   </si>
   <si>
@@ -929,12 +872,6 @@
     <t>Sis_Ativo_02</t>
   </si>
   <si>
-    <t>"[ IfcFireSuppressionTerminalSPRINKLER : IfcPipeSegment : IfcPipeFitting ]"</t>
-  </si>
-  <si>
-    <t>"[ OST_Sprinklers : OST_PipeSegments : OST_PipeFitting ]"</t>
-  </si>
-  <si>
     <t>"[ 3E.62.04 ]"</t>
   </si>
   <si>
@@ -1001,12 +938,6 @@
     <t>"[ 3E.62.20 ]"</t>
   </si>
   <si>
-    <t>"[ IfcSensorSMOKESENSOR ]"</t>
-  </si>
-  <si>
-    <t>"[ OST_FireProtection ]"</t>
-  </si>
-  <si>
     <t>"Instância de Detector de fumaça do sistema INC02 pode ser individualizado pelo ID de Revit ou pelo indentificador IfcGlobalId de IFC"</t>
   </si>
   <si>
@@ -1026,6 +957,18 @@
   </si>
   <si>
     <t>Sistemas.Prediais</t>
+  </si>
+  <si>
+    <t>"Projeto Específico de Incêndio 01"</t>
+  </si>
+  <si>
+    <t>"Um sistema do Projeto Específico de Incêndio 01"</t>
+  </si>
+  <si>
+    <t>"[ OST_FireProtection : OST_Sprinklers : OST_PipeSegments : OST_PipeFitting ]"</t>
+  </si>
+  <si>
+    <t>"[ IfcSensorSMOKESENSOR : IfcFireSuppressionTerminalSPRINKLER : IfcPipeSegment : IfcPipeFitting ]"</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1059,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1255,12 +1198,6 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1374,7 +1311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1563,14 +1500,11 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1671,14 +1605,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1724,46 +1650,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2276,15 +2162,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="56"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2292,10 +2178,10 @@
         <v>45</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2303,21 +2189,21 @@
         <v>47</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2325,10 +2211,10 @@
         <v>32</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2337,10 +2223,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2349,10 +2235,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2360,21 +2246,21 @@
         <v>53</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2382,10 +2268,10 @@
         <v>56</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2393,10 +2279,10 @@
         <v>58</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2404,10 +2290,10 @@
         <v>58</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2415,10 +2301,10 @@
         <v>58</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2426,10 +2312,10 @@
         <v>58</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2437,10 +2323,10 @@
         <v>58</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2448,10 +2334,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2459,33 +2345,33 @@
         <v>58</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46243.524946064812</v>
+        <v>46244.666254629628</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2493,10 +2379,10 @@
         <v>68</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2504,10 +2390,10 @@
         <v>58</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2515,41 +2401,41 @@
         <v>58</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Fire Fighting Objects</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2560,38 +2446,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA40"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AA35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.84375" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" style="54" customWidth="1"/>
-    <col min="5" max="5" width="10" style="54" customWidth="1"/>
-    <col min="6" max="6" width="10.15234375" style="62" customWidth="1"/>
-    <col min="7" max="11" width="6.69140625" style="54" customWidth="1"/>
-    <col min="12" max="12" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.7109375" style="54" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.69140625" style="54" customWidth="1"/>
-    <col min="16" max="16" width="83.84375" style="54" customWidth="1"/>
-    <col min="17" max="17" width="88.69140625" style="54" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.84375" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3828125" style="54" customWidth="1"/>
-    <col min="22" max="22" width="4.69140625" style="54" customWidth="1"/>
-    <col min="23" max="23" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="65.84375" style="54" customWidth="1"/>
-    <col min="25" max="25" width="35.53515625" style="55" customWidth="1"/>
-    <col min="26" max="26" width="5.53515625" style="54" customWidth="1"/>
-    <col min="27" max="27" width="82.15234375" style="54" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="54"/>
+    <col min="14" max="14" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="54" customWidth="1"/>
+    <col min="16" max="16" width="83.85546875" style="54" customWidth="1"/>
+    <col min="17" max="17" width="88.7109375" style="54" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="54" customWidth="1"/>
+    <col min="22" max="22" width="4.7109375" style="54" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="65.85546875" style="54" customWidth="1"/>
+    <col min="25" max="25" width="35.5703125" style="55" customWidth="1"/>
+    <col min="26" max="26" width="5.5703125" style="54" customWidth="1"/>
+    <col min="27" max="27" width="82.140625" style="54" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>42</v>
@@ -2624,7 +2510,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M1" s="35" t="s">
         <v>5</v>
@@ -2642,7 +2528,7 @@
         <v>43</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S1" s="35" t="s">
         <v>33</v>
@@ -2660,36 +2546,36 @@
         <v>8</v>
       </c>
       <c r="X1" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA1" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z1" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA1" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>220</v>
+        <v>293</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>231</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>83</v>
+        <v>115</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>115</v>
       </c>
       <c r="G2" s="61" t="s">
         <v>9</v>
@@ -2707,81 +2593,79 @@
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
+        <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N2" s="33" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
-      </c>
-      <c r="O2" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>85</v>
+        <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="P2" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q2" s="52" t="s">
+        <v>207</v>
       </c>
       <c r="R2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="30" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
+        <f t="shared" ref="S2:U18" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T2" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" ref="T2:U16" si="3">SUBSTITUTE(D2, ".", " ")</f>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Sistema Combate</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W2" s="59" t="str">
-        <f t="shared" ref="W2:W32" si="3">CONCATENATE("Key-INC-",A2)</f>
+        <f t="shared" ref="W2:W27" si="4">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
-      <c r="X2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="30" t="s">
-        <v>9</v>
+      <c r="X2" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y2" s="29" t="s">
+        <v>109</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA40" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="AA2:AA35" si="5">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Building Fire Fighting System</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>220</v>
+        <v>293</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>231</v>
+        <v>115</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2799,81 +2683,80 @@
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" ref="L3:M19" si="6">CONCATENATE("", C3)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M3" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N3" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O3" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
+        <f t="shared" ref="O3:O17" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
+        <v>Alarme</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="R3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T3" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" si="3"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U3" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W3" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-3</v>
       </c>
       <c r="X3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Y3" s="29" t="s">
+        <v>172</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="AA3" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Device that signals the existence of a condition or situation of danger.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>220</v>
+        <v>293</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>231</v>
+        <v>115</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -2891,81 +2774,80 @@
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="6"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M4" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N4" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O4" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
+        <f t="shared" si="7"/>
+        <v>Alarme Campainha</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="R4" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T4" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" si="3"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U4" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W4" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-4</v>
       </c>
       <c r="X4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Y4" s="29" t="s">
+        <v>173</v>
       </c>
       <c r="Z4" s="30" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="AA4" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Audible alarm.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>220</v>
+        <v>293</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>231</v>
+        <v>115</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -2983,81 +2865,80 @@
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="6"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M5" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N5" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N5" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O5" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
+        <f t="shared" si="7"/>
+        <v>Alarme Campainha Caixa</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="R5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T5" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" si="3"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U5" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W5" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-5</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Y5" s="29" t="s">
+        <v>174</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="AA5" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>220</v>
+        <v>293</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>231</v>
+        <v>115</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -3075,81 +2956,80 @@
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="6"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M6" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N6" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N6" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O6" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
+        <f t="shared" si="7"/>
+        <v>Alarme Lumínico</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>228</v>
+        <v>131</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="R6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="T6" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" si="3"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="U6" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W6" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-6</v>
       </c>
       <c r="X6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Y6" s="29" t="s">
+        <v>175</v>
       </c>
       <c r="Z6" s="30" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="AA6" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Visual light alarm.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>119</v>
+        <v>115</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>133</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -3167,79 +3047,80 @@
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
-        <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
-        <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="P7" s="52" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>214</v>
+        <v>202</v>
+      </c>
+      <c r="O7" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Alarme Caixa Manual</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="R7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="30" t="str">
-        <f t="shared" ref="S7:U23" si="7">SUBSTITUTE(C7, ".", " ")</f>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T7" s="30" t="str">
-        <f t="shared" ref="T7:U21" si="8">SUBSTITUTE(D7, ".", " ")</f>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U7" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Combate</v>
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W7" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-7</v>
       </c>
-      <c r="X7" s="29" t="s">
-        <v>111</v>
+      <c r="X7" s="30" t="s">
+        <v>166</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA7" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Building Fire Fighting System</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
@@ -3257,171 +3138,171 @@
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" ref="L8:M24" si="9">CONCATENATE("", C8)</f>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O8" s="33" t="str">
-        <f t="shared" ref="O8:O22" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
-        <v>Alarme</v>
+        <f t="shared" si="7"/>
+        <v>Alarme Detonador</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="30" t="str">
+        <f t="shared" si="2"/>
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="T8" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Sistema Incêndio</v>
+      </c>
+      <c r="U8" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Alarmes de Incêndio</v>
+      </c>
+      <c r="V8" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W8" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-INC-8</v>
+      </c>
+      <c r="X8" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y8" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z8" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA8" s="30" t="str">
+        <f t="shared" si="5"/>
+        <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="60">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M9" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="O9" s="33" t="str">
         <f t="shared" si="7"/>
+        <v>Alarme Sirene</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="30" t="str">
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T8" s="30" t="str">
-        <f t="shared" si="8"/>
+      <c r="T9" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U8" s="30" t="str">
-        <f t="shared" si="8"/>
+      <c r="U9" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V8" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W8" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-INC-8</v>
-      </c>
-      <c r="X8" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y8" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z8" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA8" s="30" t="str">
+      <c r="V9" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W9" s="59" t="str">
         <f t="shared" si="4"/>
-        <v>Device that signals the existence of a condition or situation of danger.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="60">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>317</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="33" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M9" s="33" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="O9" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Campainha</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="T9" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="U9" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="V9" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W9" s="59" t="str">
-        <f t="shared" si="3"/>
         <v>Key-INC-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA9" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Audible alarm.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Audible alarm produced by a siren.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3439,80 +3320,80 @@
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O10" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Campainha Caixa</v>
+        <f t="shared" si="7"/>
+        <v>Alarme Apito</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T10" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U10" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W10" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA10" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Audible alarm produced by a whistle.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3530,80 +3411,80 @@
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O11" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Lumínico</v>
+        <f t="shared" si="7"/>
+        <v>Terminal Combate Fogo</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="R11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T11" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U11" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
+        <f t="shared" si="3"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W11" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-11</v>
       </c>
       <c r="X11" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y11" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="Y11" s="29" t="s">
-        <v>179</v>
-      </c>
       <c r="Z11" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA11" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Visual light alarm.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3621,80 +3502,80 @@
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O12" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Caixa Manual</v>
+        <f t="shared" si="7"/>
+        <v>Mangueira Entrada</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="R12" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T12" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U12" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
+        <f t="shared" si="3"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W12" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Y12" s="29" t="s">
         <v>180</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA12" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3712,80 +3593,80 @@
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O13" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Detonador</v>
+        <f t="shared" si="7"/>
+        <v>Mangueira Carretel</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="R13" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T13" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U13" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
+        <f t="shared" si="3"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W13" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Y13" s="29" t="s">
         <v>181</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA13" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Support structure on which a hose can be wound.</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -3803,171 +3684,171 @@
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O14" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Sirene</v>
+        <f t="shared" si="7"/>
+        <v>Mangueira Canhão</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="R14" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T14" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U14" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
+        <f t="shared" si="3"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W14" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y14" s="29" t="s">
         <v>182</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA14" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Audible alarm produced by a siren.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Fire monitor.</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="33" t="str">
+        <f t="shared" ref="L15" si="8">CONCATENATE("", C15)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M15" s="33" t="str">
+        <f t="shared" ref="M15" si="9">CONCATENATE("", D15)</f>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="O15" s="33" t="str">
+        <f t="shared" ref="O15" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
+        <v>Detetor de Fumaça</v>
+      </c>
+      <c r="P15" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="F15" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="33" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M15" s="33" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N15" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="O15" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Alarme Apito</v>
-      </c>
-      <c r="P15" s="30" t="s">
-        <v>147</v>
-      </c>
       <c r="Q15" s="30" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="R15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S15" si="11">SUBSTITUTE(C15, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T15" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="T15" si="12">SUBSTITUTE(D15, ".", " ")</f>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U15" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Alarmes de Incêndio</v>
+        <f t="shared" ref="U15" si="13">SUBSTITUTE(E15, ".", " ")</f>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W15" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Y15" s="29" t="s">
         <v>183</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA15" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Audible alarm produced by a whistle.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Smoke detector.</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -3985,80 +3866,80 @@
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O16" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Terminal Combate Fogo</v>
+        <f t="shared" si="7"/>
+        <v>Hidrante</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T16" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U16" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W16" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA16" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -4076,80 +3957,80 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O17" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Mangueira Entrada</v>
+        <f t="shared" si="7"/>
+        <v>Sprinkler</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="R17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T17" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U17" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W17" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y17" s="29" t="s">
         <v>184</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA17" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>A device for spraying water from a pipe under pressure over an area.</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -4167,80 +4048,79 @@
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O18" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Mangueira Carretel</v>
+        <v>203</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>199</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="R18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T18" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U18" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W18" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y18" s="29" t="s">
         <v>185</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA18" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Support structure on which a hose can be wound.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>158</v>
+        <v>209</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>165</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4258,80 +4138,80 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O19" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Mangueira Canhão</v>
-      </c>
-      <c r="P19" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q19" s="30" t="s">
-        <v>160</v>
+        <v>203</v>
+      </c>
+      <c r="O19" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q19" s="30" t="str">
+        <f t="shared" ref="Q19" si="14">_xlfn.TRANSLATE(P19,"pt","es")</f>
+        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
       </c>
       <c r="R19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S19:U24" si="15">SUBSTITUTE(C19, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T19" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U19" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>Peças de Incêndio</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W19" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA19" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Fire monitor.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>233</v>
+        <v>115</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>117</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4349,80 +4229,80 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" ref="L20" si="11">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:L23" si="16">CONCATENATE("", C20)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" ref="M20" si="12">CONCATENATE("", D20)</f>
+        <f t="shared" ref="M20:M23" si="17">CONCATENATE("", D20)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O20" s="33" t="str">
-        <f t="shared" ref="O20" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F20),"."," ")," De "," de "))</f>
-        <v>Detetor de Fumaça</v>
-      </c>
-      <c r="P20" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q20" s="30" t="s">
-        <v>235</v>
+        <v>204</v>
+      </c>
+      <c r="O20" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="P20" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q20" s="30" t="str">
+        <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
+        <v>Cisterna Superior</v>
       </c>
       <c r="R20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="30" t="str">
-        <f t="shared" ref="S20" si="14">SUBSTITUTE(C20, ".", " ")</f>
+        <f t="shared" si="15"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" ref="T20" si="15">SUBSTITUTE(D20, ".", " ")</f>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" ref="U20" si="16">SUBSTITUTE(E20, ".", " ")</f>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W20" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-20</v>
       </c>
-      <c r="X20" s="30" t="s">
-        <v>171</v>
+      <c r="X20" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA20" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Smoke detector.</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Upper Cistern</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>161</v>
+        <v>115</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>211</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4440,80 +4320,80 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O21" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Hidrante</v>
-      </c>
-      <c r="P21" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q21" s="30" t="s">
-        <v>163</v>
+        <v>204</v>
+      </c>
+      <c r="O21" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="P21" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q21" s="30" t="str">
+        <f t="shared" ref="Q21:Q27" si="18">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Cisterna intermedia</v>
       </c>
       <c r="R21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W21" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-21</v>
       </c>
-      <c r="X21" s="30" t="s">
-        <v>171</v>
+      <c r="X21" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA21" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Intermediate Cistern</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>124</v>
+        <v>115</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>118</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4531,81 +4411,81 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O22" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>Sprinkler</v>
-      </c>
-      <c r="P22" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q22" s="30" t="s">
-        <v>165</v>
+        <v>204</v>
+      </c>
+      <c r="O22" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="P22" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q22" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Cisterna Inferior</v>
       </c>
       <c r="R22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T22" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U22" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W22" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-22</v>
       </c>
-      <c r="X22" s="30" t="s">
-        <v>173</v>
+      <c r="X22" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA22" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>A device for spraying water from a pipe under pressure over an area.</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Lower Cistern</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F23" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F23" s="57" t="s">
-        <v>166</v>
-      </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
       </c>
@@ -4622,79 +4502,80 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O23" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="P23" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q23" s="30" t="s">
-        <v>168</v>
+        <v>204</v>
+      </c>
+      <c r="O23" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="P23" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Tubería de agua fría</v>
       </c>
       <c r="R23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T23" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U23" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W23" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-23</v>
       </c>
-      <c r="X23" s="30" t="s">
-        <v>173</v>
+      <c r="X23" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA23" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Cold Water Pipe</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>216</v>
+        <v>115</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>210</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4712,80 +4593,80 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="L24:L26" si="19">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="M24:M26" si="20">CONCATENATE("", D24)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="30" t="str">
-        <f t="shared" ref="Q24" si="17">_xlfn.TRANSLATE(P24,"pt","es")</f>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
+        <f t="shared" si="18"/>
+        <v>Tubería de agua fría</v>
       </c>
       <c r="R24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S24" s="30" t="str">
-        <f t="shared" ref="S24:U29" si="18">SUBSTITUTE(C24, ".", " ")</f>
+        <f t="shared" ref="S24:S26" si="21">SUBSTITUTE(C24, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
       <c r="T24" s="30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="U24" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W24" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-24</v>
       </c>
-      <c r="X24" s="30" t="s">
-        <v>172</v>
+      <c r="X24" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA24" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Cold Water Pipe</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>121</v>
+        <v>226</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -4803,80 +4684,80 @@
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
-        <f t="shared" ref="L25:L28" si="19">CONCATENATE("", C25)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="19"/>
+        <v>De.Incêndio</v>
       </c>
       <c r="M25" s="33" t="str">
-        <f t="shared" ref="M25:M28" si="20">CONCATENATE("", D25)</f>
-        <v>Sistema.Incêndio</v>
+        <f t="shared" si="20"/>
+        <v>Sistemas.Passivos</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="O25" s="52" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="Q25" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P25,"pt","es")</f>
-        <v>Cisterna Superior</v>
+        <f t="shared" si="18"/>
+        <v>La puerta cortafuegos que se cierra impide el paso del fuego y el humo.</v>
       </c>
       <c r="R25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistemas Prediais</v>
+        <f t="shared" si="21"/>
+        <v>De Incêndio</v>
       </c>
       <c r="T25" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistema Incêndio</v>
+        <f t="shared" ref="T25:T27" si="22">SUBSTITUTE(D25, ".", " ")</f>
+        <v>Sistemas Passivos</v>
       </c>
       <c r="U25" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" ref="U25:U27" si="23">SUBSTITUTE(E25, ".", " ")</f>
+        <v>De Selagem</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W25" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>110</v>
+        <v>221</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA25" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Upper Cistern</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Fire door that closed prevents the passage of fire and smoke.</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4895,79 +4776,79 @@
       </c>
       <c r="L26" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>Sistemas.Prediais</v>
+        <v>De.Incêndio</v>
       </c>
       <c r="M26" s="33" t="str">
         <f t="shared" si="20"/>
-        <v>Sistema.Incêndio</v>
+        <v>Sistemas.Passivos</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="P26" s="52" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="Q26" s="30" t="str">
-        <f t="shared" ref="Q26:Q32" si="21">_xlfn.TRANSLATE(P26,"pt","es")</f>
-        <v>Cisterna intermedia</v>
+        <f t="shared" si="18"/>
+        <v>Muros y tabiques que limitan la propagación de las llamas gracias a sus propiedades de resistencia al fuego, diseñados específicamente para esta función.</v>
       </c>
       <c r="R26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistemas Prediais</v>
+        <f t="shared" si="21"/>
+        <v>De Incêndio</v>
       </c>
       <c r="T26" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistema Incêndio</v>
+        <f t="shared" si="22"/>
+        <v>Sistemas Passivos</v>
       </c>
       <c r="U26" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="23"/>
+        <v>De Selagem</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W26" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA26" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Intermediate Cistern</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>122</v>
+        <v>227</v>
       </c>
       <c r="G27" s="61" t="s">
         <v>9</v>
@@ -4985,80 +4866,80 @@
         <v>9</v>
       </c>
       <c r="L27" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" ref="L27:L29" si="24">CONCATENATE("", C27)</f>
+        <v>De.Incêndio</v>
       </c>
       <c r="M27" s="33" t="str">
-        <f t="shared" si="20"/>
-        <v>Sistema.Incêndio</v>
+        <f t="shared" ref="M27:M29" si="25">CONCATENATE("", D27)</f>
+        <v>Sistemas.Passivos</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="O27" s="52" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="Q27" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Cisterna Inferior</v>
+        <f t="shared" si="18"/>
+        <v>Pozos y pasadizos verticales diseñados con sellado intumescente, volcadores sin humo y barreras cortafuego en cada planta.</v>
       </c>
       <c r="R27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistemas Prediais</v>
+        <f t="shared" ref="S27:S29" si="26">SUBSTITUTE(C27, ".", " ")</f>
+        <v>De Incêndio</v>
       </c>
       <c r="T27" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistema Incêndio</v>
+        <f t="shared" si="22"/>
+        <v>Sistemas Passivos</v>
       </c>
       <c r="U27" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="23"/>
+        <v>De Selagem</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W27" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Key-INC-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="Z27" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA27" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Lower Cistern</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
@@ -5076,80 +4957,80 @@
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" ref="L28" si="27">CONCATENATE("", C28)</f>
+        <v>De.Incêndio</v>
       </c>
       <c r="M28" s="33" t="str">
-        <f t="shared" si="20"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N28" s="33" t="s">
-        <v>211</v>
+        <f t="shared" ref="M28" si="28">CONCATENATE("", D28)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N28" s="52" t="s">
+        <v>242</v>
       </c>
       <c r="O28" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="P28" s="52" t="s">
-        <v>108</v>
+        <v>239</v>
+      </c>
+      <c r="P28" s="63" t="s">
+        <v>243</v>
       </c>
       <c r="Q28" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubería de agua fría</v>
+        <f t="shared" ref="Q28:Q30" si="29">_xlfn.TRANSLATE(P28,"pt","es")</f>
+        <v>El colgante de aspersores es una ducha automática instalada en el techo con el chorro de agua hacia abajo.</v>
       </c>
       <c r="R28" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S28" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistemas Prediais</v>
+        <f t="shared" ref="S28" si="30">SUBSTITUTE(C28, ".", " ")</f>
+        <v>De Incêndio</v>
       </c>
       <c r="T28" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistema Incêndio</v>
+        <f t="shared" ref="T28:T30" si="31">SUBSTITUTE(D28, ".", " ")</f>
+        <v>Sistemas Ativos</v>
       </c>
       <c r="U28" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" ref="U28:U30" si="32">SUBSTITUTE(E28, ".", " ")</f>
+        <v>De Combate</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W28" s="59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W28:W30" si="33">CONCATENATE("Key-INC-",A28)</f>
         <v>Key-INC-28</v>
       </c>
-      <c r="X28" s="29" t="s">
-        <v>269</v>
+      <c r="X28" s="30" t="s">
+        <v>251</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA28" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
@@ -5167,353 +5048,353 @@
         <v>9</v>
       </c>
       <c r="L29" s="33" t="str">
-        <f t="shared" ref="L29:L31" si="22">CONCATENATE("", C29)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="24"/>
+        <v>De.Incêndio</v>
       </c>
       <c r="M29" s="33" t="str">
-        <f t="shared" ref="M29:M31" si="23">CONCATENATE("", D29)</f>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N29" s="33" t="s">
-        <v>211</v>
+        <f t="shared" si="25"/>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N29" s="52" t="s">
+        <v>242</v>
       </c>
       <c r="O29" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="P29" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q29" s="30" t="str">
+        <f t="shared" ref="Q29" si="34">_xlfn.TRANSLATE(P29,"pt","es")</f>
+        <v>El rociador vertical es una ducha automática instalada en tuberías expuestas bajo el techo con el chorro de agua hacia arriba.</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="30" t="str">
+        <f t="shared" si="26"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" ref="T29" si="35">SUBSTITUTE(D29, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" ref="U29" si="36">SUBSTITUTE(E29, ".", " ")</f>
+        <v>De Combate</v>
+      </c>
+      <c r="V29" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W29" s="59" t="str">
+        <f t="shared" ref="W29" si="37">CONCATENATE("Key-INC-",A29)</f>
+        <v>Key-INC-29</v>
+      </c>
+      <c r="X29" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y29" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z29" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="P29" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q29" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubería de agua fría</v>
-      </c>
-      <c r="R29" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="30" t="str">
-        <f t="shared" ref="S29:S31" si="24">SUBSTITUTE(C29, ".", " ")</f>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="T29" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="U29" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubulação de Incêndio</v>
-      </c>
-      <c r="V29" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W29" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-INC-29</v>
-      </c>
-      <c r="X29" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y29" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z29" s="30" t="s">
-        <v>212</v>
-      </c>
       <c r="AA29" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
+        <f t="shared" ref="L30" si="38">CONCATENATE("", C30)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M30" s="33" t="str">
+        <f t="shared" ref="M30" si="39">CONCATENATE("", D30)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N30" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="O30" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="P30" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q30" s="30" t="str">
+        <f t="shared" si="29"/>
+        <v>El rociador lateral es una ducha automática instalada en las paredes, ideal para pasillos.</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="30" t="str">
+        <f t="shared" ref="S30" si="40">SUBSTITUTE(C30, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" si="31"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" si="32"/>
+        <v>De Combate</v>
+      </c>
+      <c r="V30" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W30" s="59" t="str">
+        <f t="shared" si="33"/>
+        <v>Key-INC-30</v>
+      </c>
+      <c r="X30" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="33" t="str">
-        <f t="shared" si="22"/>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M30" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N30" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="O30" s="52" t="s">
-        <v>243</v>
-      </c>
-      <c r="P30" s="52" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q30" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>La puerta cortafuegos que se cierra impide el paso del fuego y el humo.</v>
-      </c>
-      <c r="R30" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="30" t="str">
-        <f t="shared" si="24"/>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T30" s="30" t="str">
-        <f t="shared" ref="T30:T32" si="25">SUBSTITUTE(D30, ".", " ")</f>
-        <v>Sistemas Passivos</v>
-      </c>
-      <c r="U30" s="30" t="str">
-        <f t="shared" ref="U30:U32" si="26">SUBSTITUTE(E30, ".", " ")</f>
-        <v>De Selagem</v>
-      </c>
-      <c r="V30" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W30" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-INC-30</v>
-      </c>
-      <c r="X30" s="29" t="s">
-        <v>239</v>
-      </c>
       <c r="Y30" s="29" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA30" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Fire door that closed prevents the passage of fire and smoke.</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="33" t="str">
+        <f t="shared" ref="L31" si="41">CONCATENATE("", C31)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M31" s="33" t="str">
+        <f t="shared" ref="M31" si="42">CONCATENATE("", D31)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N31" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="O31" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="P31" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q31" s="30" t="str">
+        <f t="shared" ref="Q31" si="43">_xlfn.TRANSLATE(P31,"pt","es")</f>
+        <v>Detecta partículas muy pequeñas de humo en incendios de combustión rápida.</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="30" t="str">
+        <f t="shared" ref="S31" si="44">SUBSTITUTE(C31, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T31" s="30" t="str">
+        <f t="shared" ref="T31" si="45">SUBSTITUTE(D31, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U31" s="30" t="str">
+        <f t="shared" ref="U31" si="46">SUBSTITUTE(E31, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V31" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W31" s="59" t="str">
+        <f t="shared" ref="W31" si="47">CONCATENATE("Key-INC-",A31)</f>
+        <v>Key-INC-31</v>
+      </c>
+      <c r="X31" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="E31" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="F31" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="G31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L31" s="33" t="str">
-        <f t="shared" si="22"/>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M31" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N31" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="O31" s="52" t="s">
-        <v>242</v>
-      </c>
-      <c r="P31" s="52" t="s">
+      <c r="Y31" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="Q31" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Muros y tabiques que limitan la propagación de las llamas gracias a sus propiedades de resistencia al fuego, diseñados específicamente para esta función.</v>
-      </c>
-      <c r="R31" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="30" t="str">
-        <f t="shared" si="24"/>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T31" s="30" t="str">
-        <f t="shared" si="25"/>
-        <v>Sistemas Passivos</v>
-      </c>
-      <c r="U31" s="30" t="str">
-        <f t="shared" si="26"/>
-        <v>De Selagem</v>
-      </c>
-      <c r="V31" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W31" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-INC-31</v>
-      </c>
-      <c r="X31" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y31" s="29" t="s">
-        <v>9</v>
-      </c>
       <c r="Z31" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA31" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Detects very small particles of smoke in fast-burning fires.</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="33" t="str">
+        <f t="shared" ref="L32:L33" si="48">CONCATENATE("", C32)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M32" s="33" t="str">
+        <f t="shared" ref="M32:M33" si="49">CONCATENATE("", D32)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N32" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" s="52" t="s">
+        <v>277</v>
+      </c>
+      <c r="P32" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q32" s="30" t="str">
+        <f t="shared" ref="Q32:Q33" si="50">_xlfn.TRANSLATE(P32,"pt","es")</f>
+        <v>Detecta el humo dispersando la luz en una cámara interna. Más efectivo en incendios latentes (humo denso). Es el tipo más común en edificios residenciales y comerciales.</v>
+      </c>
+      <c r="R32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S32" s="30" t="str">
+        <f t="shared" ref="S32:S33" si="51">SUBSTITUTE(C32, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="T32" s="30" t="str">
+        <f t="shared" ref="T32:T33" si="52">SUBSTITUTE(D32, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="U32" s="30" t="str">
+        <f t="shared" ref="U32:U33" si="53">SUBSTITUTE(E32, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="V32" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="W32" s="59" t="str">
+        <f t="shared" ref="W32:W33" si="54">CONCATENATE("Key-INC-",A32)</f>
+        <v>Key-INC-32</v>
+      </c>
+      <c r="X32" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="E32" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="F32" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="G32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L32" s="33" t="str">
-        <f t="shared" ref="L32:L34" si="27">CONCATENATE("", C32)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M32" s="33" t="str">
-        <f t="shared" ref="M32:M34" si="28">CONCATENATE("", D32)</f>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N32" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="O32" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="P32" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q32" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Pozos y pasadizos verticales diseñados con sellado intumescente, volcadores sin humo y barreras cortafuego en cada planta.</v>
-      </c>
-      <c r="R32" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="30" t="str">
-        <f t="shared" ref="S32:S34" si="29">SUBSTITUTE(C32, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T32" s="30" t="str">
-        <f t="shared" si="25"/>
-        <v>Sistemas Passivos</v>
-      </c>
-      <c r="U32" s="30" t="str">
-        <f t="shared" si="26"/>
-        <v>De Selagem</v>
-      </c>
-      <c r="V32" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W32" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-INC-32</v>
-      </c>
-      <c r="X32" s="29" t="s">
-        <v>266</v>
-      </c>
       <c r="Y32" s="29" t="s">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="Z32" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA32" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="G33" s="61" t="s">
         <v>9</v>
@@ -5531,80 +5412,80 @@
         <v>9</v>
       </c>
       <c r="L33" s="33" t="str">
-        <f t="shared" ref="L33" si="30">CONCATENATE("", C33)</f>
+        <f t="shared" si="48"/>
         <v>De.Incêndio</v>
       </c>
       <c r="M33" s="33" t="str">
-        <f t="shared" ref="M33" si="31">CONCATENATE("", D33)</f>
+        <f t="shared" si="49"/>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N33" s="52" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O33" s="52" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="P33" s="63" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="Q33" s="30" t="str">
-        <f t="shared" ref="Q33:Q35" si="32">_xlfn.TRANSLATE(P33,"pt","es")</f>
-        <v>El colgante de aspersores es una ducha automática instalada en el techo con el chorro de agua hacia abajo.</v>
+        <f t="shared" si="50"/>
+        <v>Detecta el uso de una red de tuberías que succiona continuamente aire del entorno. Detecta partículas muy pequeñas, permitiendo una detección temprana. Ideal para centros de datos, museos, bibliotecas y entornos críticos.</v>
       </c>
       <c r="R33" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S33" s="30" t="str">
-        <f t="shared" ref="S33" si="33">SUBSTITUTE(C33, ".", " ")</f>
+        <f t="shared" si="51"/>
         <v>De Incêndio</v>
       </c>
       <c r="T33" s="30" t="str">
-        <f t="shared" ref="T33:T35" si="34">SUBSTITUTE(D33, ".", " ")</f>
+        <f t="shared" si="52"/>
         <v>Sistemas Ativos</v>
       </c>
       <c r="U33" s="30" t="str">
-        <f t="shared" ref="U33:U35" si="35">SUBSTITUTE(E33, ".", " ")</f>
-        <v>De Combate</v>
+        <f t="shared" si="53"/>
+        <v>De Detecção</v>
       </c>
       <c r="V33" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W33" s="59" t="str">
-        <f t="shared" ref="W33:W35" si="36">CONCATENATE("Key-INC-",A33)</f>
+        <f t="shared" si="54"/>
         <v>Key-INC-33</v>
       </c>
       <c r="X33" s="30" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="Y33" s="29" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="Z33" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA33" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="G34" s="61" t="s">
         <v>9</v>
@@ -5622,80 +5503,80 @@
         <v>9</v>
       </c>
       <c r="L34" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="L34" si="55">CONCATENATE("", C34)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M34" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="M34" si="56">CONCATENATE("", D34)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N34" s="52" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O34" s="52" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="P34" s="63" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="Q34" s="30" t="str">
-        <f t="shared" ref="Q34" si="37">_xlfn.TRANSLATE(P34,"pt","es")</f>
-        <v>El rociador vertical es una ducha automática instalada en tuberías expuestas bajo el techo con el chorro de agua hacia arriba.</v>
+        <f t="shared" ref="Q34" si="57">_xlfn.TRANSLATE(P34,"pt","es")</f>
+        <v>Detecta gracias a un haz de luz (láser o infrarrojo) entre el emisor y el receptor.</v>
       </c>
       <c r="R34" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S34" s="30" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="S34" si="58">SUBSTITUTE(C34, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
       <c r="T34" s="30" t="str">
-        <f t="shared" ref="T34" si="38">SUBSTITUTE(D34, ".", " ")</f>
+        <f t="shared" ref="T34" si="59">SUBSTITUTE(D34, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
       <c r="U34" s="30" t="str">
-        <f t="shared" ref="U34" si="39">SUBSTITUTE(E34, ".", " ")</f>
-        <v>De Combate</v>
+        <f t="shared" ref="U34" si="60">SUBSTITUTE(E34, ".", " ")</f>
+        <v>De Detecção</v>
       </c>
       <c r="V34" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W34" s="59" t="str">
-        <f t="shared" ref="W34" si="40">CONCATENATE("Key-INC-",A34)</f>
+        <f t="shared" ref="W34" si="61">CONCATENATE("Key-INC-",A34)</f>
         <v>Key-INC-34</v>
       </c>
       <c r="X34" s="30" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="Y34" s="29" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="Z34" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA34" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="G35" s="61" t="s">
         <v>9</v>
@@ -5713,582 +5594,116 @@
         <v>9</v>
       </c>
       <c r="L35" s="33" t="str">
-        <f t="shared" ref="L35" si="41">CONCATENATE("", C35)</f>
+        <f t="shared" ref="L35" si="62">CONCATENATE("", C35)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M35" s="33" t="str">
-        <f t="shared" ref="M35" si="42">CONCATENATE("", D35)</f>
+        <f t="shared" ref="M35" si="63">CONCATENATE("", D35)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N35" s="52" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="O35" s="52" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="P35" s="63" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="Q35" s="30" t="str">
-        <f t="shared" si="32"/>
-        <v>El rociador lateral es una ducha automática instalada en las paredes, ideal para pasillos.</v>
+        <f t="shared" ref="Q35" si="64">_xlfn.TRANSLATE(P35,"pt","es")</f>
+        <v>Detector que integra detección de humo y calor en el mismo dispositivo. Aumenta la fiabilidad, estando indicado para entornos industriales o con variaciones de temperatura.</v>
       </c>
       <c r="R35" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S35" s="30" t="str">
-        <f t="shared" ref="S35" si="43">SUBSTITUTE(C35, ".", " ")</f>
+        <f t="shared" ref="S35" si="65">SUBSTITUTE(C35, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
       <c r="T35" s="30" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="T35" si="66">SUBSTITUTE(D35, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
       <c r="U35" s="30" t="str">
-        <f t="shared" si="35"/>
-        <v>De Combate</v>
+        <f t="shared" ref="U35" si="67">SUBSTITUTE(E35, ".", " ")</f>
+        <v>De Detecção</v>
       </c>
       <c r="V35" s="30" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="W35" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="W35" si="68">CONCATENATE("Key-INC-",A35)</f>
         <v>Key-INC-35</v>
       </c>
       <c r="X35" s="30" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="Y35" s="29" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="Z35" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AA35" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="60">
-        <v>36</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="G36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="33" t="str">
-        <f t="shared" ref="L36" si="44">CONCATENATE("", C36)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M36" s="33" t="str">
-        <f t="shared" ref="M36" si="45">CONCATENATE("", D36)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N36" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="O36" s="52" t="s">
-        <v>297</v>
-      </c>
-      <c r="P36" s="63" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q36" s="30" t="str">
-        <f t="shared" ref="Q36" si="46">_xlfn.TRANSLATE(P36,"pt","es")</f>
-        <v>Detecta partículas muy pequeñas de humo en incendios de combustión rápida.</v>
-      </c>
-      <c r="R36" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S36" s="30" t="str">
-        <f t="shared" ref="S36" si="47">SUBSTITUTE(C36, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T36" s="30" t="str">
-        <f t="shared" ref="T36" si="48">SUBSTITUTE(D36, ".", " ")</f>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U36" s="30" t="str">
-        <f t="shared" ref="U36" si="49">SUBSTITUTE(E36, ".", " ")</f>
-        <v>De Detecção</v>
-      </c>
-      <c r="V36" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W36" s="59" t="str">
-        <f t="shared" ref="W36" si="50">CONCATENATE("Key-INC-",A36)</f>
-        <v>Key-INC-36</v>
-      </c>
-      <c r="X36" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y36" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z36" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA36" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Detects very small particles of smoke in fast-burning fires.</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="60">
-        <v>37</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="G37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L37" s="33" t="str">
-        <f t="shared" ref="L37:L38" si="51">CONCATENATE("", C37)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M37" s="33" t="str">
-        <f t="shared" ref="M37:M38" si="52">CONCATENATE("", D37)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N37" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="O37" s="52" t="s">
-        <v>298</v>
-      </c>
-      <c r="P37" s="63" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q37" s="30" t="str">
-        <f t="shared" ref="Q37:Q38" si="53">_xlfn.TRANSLATE(P37,"pt","es")</f>
-        <v>Detecta el humo dispersando la luz en una cámara interna. Más efectivo en incendios latentes (humo denso). Es el tipo más común en edificios residenciales y comerciales.</v>
-      </c>
-      <c r="R37" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S37" s="30" t="str">
-        <f t="shared" ref="S37:S38" si="54">SUBSTITUTE(C37, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T37" s="30" t="str">
-        <f t="shared" ref="T37:T38" si="55">SUBSTITUTE(D37, ".", " ")</f>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U37" s="30" t="str">
-        <f t="shared" ref="U37:U38" si="56">SUBSTITUTE(E37, ".", " ")</f>
-        <v>De Detecção</v>
-      </c>
-      <c r="V37" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W37" s="59" t="str">
-        <f t="shared" ref="W37:W38" si="57">CONCATENATE("Key-INC-",A37)</f>
-        <v>Key-INC-37</v>
-      </c>
-      <c r="X37" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y37" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z37" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA37" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="60">
-        <v>38</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="G38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M38" s="33" t="str">
-        <f t="shared" si="52"/>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N38" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="O38" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="P38" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q38" s="30" t="str">
-        <f t="shared" si="53"/>
-        <v>Detecta el uso de una red de tuberías que succiona continuamente aire del entorno. Detecta partículas muy pequeñas, permitiendo una detección temprana. Ideal para centros de datos, museos, bibliotecas y entornos críticos.</v>
-      </c>
-      <c r="R38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S38" s="30" t="str">
-        <f t="shared" si="54"/>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T38" s="30" t="str">
-        <f t="shared" si="55"/>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U38" s="30" t="str">
-        <f t="shared" si="56"/>
-        <v>De Detecção</v>
-      </c>
-      <c r="V38" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W38" s="59" t="str">
-        <f t="shared" si="57"/>
-        <v>Key-INC-38</v>
-      </c>
-      <c r="X38" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y38" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z38" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA38" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="60">
-        <v>39</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="G39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" s="33" t="str">
-        <f t="shared" ref="L39" si="58">CONCATENATE("", C39)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M39" s="33" t="str">
-        <f t="shared" ref="M39" si="59">CONCATENATE("", D39)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N39" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="O39" s="52" t="s">
-        <v>300</v>
-      </c>
-      <c r="P39" s="63" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q39" s="30" t="str">
-        <f t="shared" ref="Q39" si="60">_xlfn.TRANSLATE(P39,"pt","es")</f>
-        <v>Detecta gracias a un haz de luz (láser o infrarrojo) entre el emisor y el receptor.</v>
-      </c>
-      <c r="R39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S39" s="30" t="str">
-        <f t="shared" ref="S39" si="61">SUBSTITUTE(C39, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T39" s="30" t="str">
-        <f t="shared" ref="T39" si="62">SUBSTITUTE(D39, ".", " ")</f>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U39" s="30" t="str">
-        <f t="shared" ref="U39" si="63">SUBSTITUTE(E39, ".", " ")</f>
-        <v>De Detecção</v>
-      </c>
-      <c r="V39" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W39" s="59" t="str">
-        <f t="shared" ref="W39" si="64">CONCATENATE("Key-INC-",A39)</f>
-        <v>Key-INC-39</v>
-      </c>
-      <c r="X39" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y39" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z39" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA39" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="60">
-        <v>40</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="G40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L40" s="33" t="str">
-        <f t="shared" ref="L40" si="65">CONCATENATE("", C40)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M40" s="33" t="str">
-        <f t="shared" ref="M40" si="66">CONCATENATE("", D40)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N40" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="O40" s="52" t="s">
-        <v>301</v>
-      </c>
-      <c r="P40" s="63" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q40" s="30" t="str">
-        <f t="shared" ref="Q40" si="67">_xlfn.TRANSLATE(P40,"pt","es")</f>
-        <v>Detector que integra detección de humo y calor en el mismo dispositivo. Aumenta la fiabilidad, estando indicado para entornos industriales o con variaciones de temperatura.</v>
-      </c>
-      <c r="R40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S40" s="30" t="str">
-        <f t="shared" ref="S40" si="68">SUBSTITUTE(C40, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T40" s="30" t="str">
-        <f t="shared" ref="T40" si="69">SUBSTITUTE(D40, ".", " ")</f>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U40" s="30" t="str">
-        <f t="shared" ref="U40" si="70">SUBSTITUTE(E40, ".", " ")</f>
-        <v>De Detecção</v>
-      </c>
-      <c r="V40" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="W40" s="59" t="str">
-        <f t="shared" ref="W40" si="71">CONCATENATE("Key-INC-",A40)</f>
-        <v>Key-INC-40</v>
-      </c>
-      <c r="X40" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y40" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z40" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA40" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Detector that integrates smoke and heat detection in the same device. Increases reliability, being indicated for industrial environments or with temperature variations.</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA888">
-    <sortCondition ref="F7:F888"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA883">
+    <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B40">
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA35 A2:B35">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7 F24:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="1536"/>
+  <conditionalFormatting sqref="F1:F2 F19:F1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="26" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1514"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="25" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+  <conditionalFormatting sqref="F3:F18">
+    <cfRule type="duplicateValues" dxfId="20" priority="1558"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F23">
-    <cfRule type="duplicateValues" dxfId="21" priority="1558"/>
+  <conditionalFormatting sqref="F36:F1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1507"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1486"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1507"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O21:O23 A1:D1 F1:O1 Q1:X1 Z1:AA1 E8:F20 L8:O20 Q8:Q23 X8:Y23 AB8:XFD23 F21:F23 L21:M23 E21:E24 N21:N24">
-    <cfRule type="cellIs" dxfId="16" priority="78" operator="equal">
+  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:X1 Z1:AA1 E3:F15 L3:O15 Q3:Q18 X3:Y18 AB3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
+    <cfRule type="cellIs" dxfId="15" priority="78" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23">
-    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
+  <conditionalFormatting sqref="O18">
+    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O24:O32">
-    <cfRule type="duplicateValues" dxfId="14" priority="1565"/>
+  <conditionalFormatting sqref="O19:O27">
+    <cfRule type="duplicateValues" dxfId="13" priority="1565"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O33:O40">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+  <conditionalFormatting sqref="O28:O35">
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7">
-    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="duplicateValues" dxfId="11" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S40">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+  <conditionalFormatting sqref="S2:S35">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X24">
-    <cfRule type="cellIs" dxfId="10" priority="30" operator="equal">
+  <conditionalFormatting sqref="X19">
+    <cfRule type="cellIs" dxfId="9" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X33:X40">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA40">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+  <conditionalFormatting sqref="X28:X35">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6300,15 +5715,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6373,7 +5788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6438,7 +5853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6521,15 +5936,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6552,7 +5967,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6608,30 +6023,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" customWidth="1"/>
-    <col min="3" max="3" width="10.3828125" customWidth="1"/>
-    <col min="4" max="4" width="7.84375" customWidth="1"/>
-    <col min="5" max="5" width="7.53515625" customWidth="1"/>
-    <col min="6" max="6" width="5.15234375" customWidth="1"/>
-    <col min="7" max="7" width="56.15234375" customWidth="1"/>
-    <col min="8" max="8" width="5.15234375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="56.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.84375" customWidth="1"/>
-    <col min="11" max="11" width="18.69140625" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.3828125" customWidth="1"/>
-    <col min="14" max="14" width="6.69140625" customWidth="1"/>
-    <col min="15" max="15" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
-    <col min="17" max="17" width="31.84375" customWidth="1"/>
-    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.3828125" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" customWidth="1"/>
+    <col min="15" max="15" width="33.5703125" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" customWidth="1"/>
+    <col min="17" max="17" width="42.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6690,15 +6105,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>9</v>
@@ -6710,7 +6125,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="H2" s="49" t="s">
         <v>9</v>
@@ -6749,33 +6164,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -6793,7 +6208,7 @@
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>9</v>
@@ -6805,36 +6220,36 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>82</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J4" s="49" t="s">
         <v>9</v>
@@ -6852,7 +6267,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>9</v>
@@ -6864,1069 +6279,1069 @@
         <v>9</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M5" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N5" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P5" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="R5" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L6" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N6" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P6" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="R6" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N7" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R7" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H8" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L8" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N8" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P8" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R8" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K9" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L9" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N9" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R9" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L10" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N10" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P10" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R10" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L11" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N11" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P11" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R11" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H12" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N12" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P12" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R12" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H13" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L13" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M13" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N13" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P13" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R13" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H14" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L14" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N14" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P14" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R14" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L15" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N15" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R15" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N16" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P16" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R16" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N17" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P17" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R17" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H18" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L18" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N18" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P18" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R18" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H19" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L19" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M19" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N19" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P19" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R19" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="J20" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L20" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M20" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N20" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="P20" s="49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="R20" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="H21" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="L21" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N21" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O21" s="24" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P21" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q21" s="64" t="s">
-        <v>309</v>
+        <v>99</v>
+      </c>
+      <c r="Q21" s="24" t="s">
+        <v>298</v>
       </c>
       <c r="R21" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="H22" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="J22" s="49" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="L22" s="49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N22" s="49" t="s">
         <v>100</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P22" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q22" s="64" t="s">
-        <v>309</v>
+        <v>99</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>298</v>
       </c>
       <c r="R22" s="49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
